--- a/2026/BELGRANO 1646/Marzo/Marzo-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Marzo/Marzo-BLG1646.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59285F6A-75EA-4718-B201-871B56B873D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA8456E-447B-4145-9F52-D3EEA3206FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$121</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="147">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -358,9 +363,6 @@
     <t>BALBOA, ARIEL</t>
   </si>
   <si>
-    <t>Articulos de limpieza - Montoya Alejandra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sr. Diego Britez </t>
   </si>
   <si>
@@ -379,40 +381,16 @@
     <t>Macarena</t>
   </si>
   <si>
-    <t xml:space="preserve">Fumigacion </t>
-  </si>
-  <si>
     <t>Subidos en en3r0 de 2026</t>
   </si>
   <si>
     <t>RODRIGUEZ, JORGE AGUSTIN</t>
   </si>
   <si>
-    <t>Pago mis cuentas 04/2</t>
-  </si>
-  <si>
-    <t>Debito 04/02</t>
-  </si>
-  <si>
-    <t>Reemplazo Sr. Diego (Por enfermedad) Sra Monica</t>
-  </si>
-  <si>
-    <t>Debito 12/02</t>
-  </si>
-  <si>
     <t>Fabian antonio Vivas - Trabajo en zona de pileta - Ausencias de Diego y vacaciones de Diciembre</t>
   </si>
   <si>
-    <t>La factura llego en $0</t>
-  </si>
-  <si>
     <t>Articulos de limpieza - Montoya Alejandra - Para pileta: cloro, clarificador, alargue.</t>
-  </si>
-  <si>
-    <t>Seguro Sra. Monica</t>
-  </si>
-  <si>
-    <t>Reemplazo Sr. Diego (Por vacacciones) Sra Monica</t>
   </si>
   <si>
     <t>Sum - Gastos Part.</t>
@@ -462,9 +440,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>VTO: 17/04</t>
   </si>
   <si>
@@ -487,6 +462,48 @@
   </si>
   <si>
     <t>BORRAR A MAURO MARANTE DE MAILS</t>
+  </si>
+  <si>
+    <t>Renovacion de Wifi y Cable (2 bocas) anual</t>
+  </si>
+  <si>
+    <t>Debito 04/3</t>
+  </si>
+  <si>
+    <t>Fumigacion - Mes de febrero</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 09/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tofema - Compra de materiales </t>
+  </si>
+  <si>
+    <t>Debito 12/03</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Montoya Alejandra -  Cloro, alguicida, clarificador</t>
+  </si>
+  <si>
+    <t>Pago 20/03</t>
+  </si>
+  <si>
+    <t>Gustavo Padron contador - Presentacion Balance RPAC</t>
+  </si>
+  <si>
+    <t>Fumigacion - Mes de marzo</t>
+  </si>
+  <si>
+    <t>Destapacion AySa - Pago en efectivo</t>
+  </si>
+  <si>
+    <t>Alterini - Jardineria - Maceta premium, tierra fertil, mantenimiento</t>
+  </si>
+  <si>
+    <t>Se adeuda mes de Marzo</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Montoya Alejandra - Cif, liquido para pisos, guantes, etc</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1063,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
@@ -1091,7 +1108,6 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1099,7 +1115,6 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1212,9 +1227,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1232,7 +1244,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1302,24 +1313,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1329,6 +1322,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1398,8 +1394,38 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1480,9 +1506,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1520,9 +1546,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1555,9 +1581,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1590,9 +1633,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1766,359 +1826,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N131"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="96"/>
-      <c r="B1" s="149" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="94"/>
+      <c r="B1" s="145" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="150"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="146"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
-      <c r="B2" s="113" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="114"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="111" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
-    </row>
-    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112"/>
+    </row>
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
-      <c r="B4" s="113" t="s">
+      <c r="B4" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="114"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="112"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="113" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="114"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="111" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="111" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="112"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="113"/>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="114"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="117" t="s">
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="115" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="115"/>
-      <c r="F7" s="116"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-    </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="83"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="83"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="83"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="83"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="83"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="83"/>
-      <c r="B14" s="153" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="154"/>
-      <c r="D14" s="155"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="83"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="158"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="83"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="157"/>
-      <c r="D16" s="158"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="83"/>
-      <c r="B17" s="159"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="161"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="83"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="119"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="83"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="120" t="s">
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="114"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="81"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="81"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="81"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="81"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="81"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="81"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="81"/>
+      <c r="B14" s="149" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="150"/>
+      <c r="D14" s="151"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="81"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="154"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="81"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="154"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="81"/>
+      <c r="B17" s="155"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="157"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="81"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="117"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="81"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="121"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="89" t="s">
+      <c r="B21" s="119"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="90" t="s">
+      <c r="F21" s="88" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="124" t="s">
-        <v>111</v>
-      </c>
-      <c r="B22" s="84" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="88"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="124" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="122" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="82"/>
+      <c r="D22" s="196"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="122" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="108">
-        <v>1568057.71</v>
-      </c>
-      <c r="E23" s="54">
+      <c r="B23" s="82"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="106">
+        <v>1555858.84</v>
+      </c>
+      <c r="E23" s="52">
         <f>D23*91.91%</f>
-        <v>1441201.8412609999</v>
-      </c>
-      <c r="F23" s="54">
+        <v>1429989.8598439998</v>
+      </c>
+      <c r="F23" s="52">
         <f>D23*8.09%</f>
-        <v>126855.868739</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="124" t="s">
+        <v>125868.98015600001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="108">
-        <v>-341052.55</v>
-      </c>
-      <c r="E24" s="54">
+      <c r="B24" s="82"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="106">
+        <v>-338399.31</v>
+      </c>
+      <c r="E24" s="52">
         <f t="shared" ref="E24:E26" si="0">D24*91.91%</f>
-        <v>-313461.39870499994</v>
-      </c>
-      <c r="F24" s="54">
+        <v>-311022.80582099996</v>
+      </c>
+      <c r="F24" s="52">
         <f t="shared" ref="F24:F26" si="1">D24*8.09%</f>
-        <v>-27591.151295</v>
+        <v>-27376.504179</v>
       </c>
       <c r="G24" s="36"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="124" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="108">
-        <v>0.84</v>
-      </c>
-      <c r="E25" s="54">
+      <c r="B25" s="82"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="106">
+        <v>0.47</v>
+      </c>
+      <c r="E25" s="52">
         <f t="shared" si="0"/>
-        <v>0.77204399999999995</v>
-      </c>
-      <c r="F25" s="54">
+        <v>0.43197699999999994</v>
+      </c>
+      <c r="F25" s="52">
         <f t="shared" si="1"/>
-        <v>6.7956000000000003E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="124"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="108"/>
-      <c r="E26" s="54">
+        <v>3.8022999999999994E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="122"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="52">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="125" t="s">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="125"/>
-      <c r="C27" s="125"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="123"/>
       <c r="D27" s="35">
         <f>SUM(D23:D26)</f>
-        <v>1227006</v>
+        <v>1217460</v>
       </c>
       <c r="E27" s="35">
         <f>SUM(E23:E26)</f>
-        <v>1127741.2145999998</v>
+        <v>1118967.486</v>
       </c>
       <c r="F27" s="35">
         <f>SUM(F23:F26)</f>
-        <v>99264.785399999993</v>
+        <v>98492.51400000001</v>
       </c>
       <c r="G27" s="36">
         <f>E27+F27</f>
-        <v>1227005.9999999998</v>
-      </c>
-      <c r="H27" s="66" t="str">
+        <v>1217460</v>
+      </c>
+      <c r="H27" s="64" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="126" t="s">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="84"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="109">
-        <v>0</v>
-      </c>
-      <c r="E28" s="54">
+      <c r="B28" s="82"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="107">
+        <v>0</v>
+      </c>
+      <c r="E28" s="52">
         <f>D28*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F28" s="54">
+      <c r="F28" s="52">
         <f>D28*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H28" s="66"/>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="126"/>
-      <c r="B29" s="84"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="108">
-        <v>0</v>
-      </c>
-      <c r="E29" s="54">
+      <c r="H28" s="64"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="124"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="106">
+        <v>0</v>
+      </c>
+      <c r="E29" s="52">
         <f>D29*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F29" s="54">
+      <c r="F29" s="52">
         <f>D29*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H29" s="66"/>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="126"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="108"/>
+      <c r="H29" s="64"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="124"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="106"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="H30" s="66"/>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="126"/>
-      <c r="B31" s="84"/>
-      <c r="C31" s="84"/>
-      <c r="D31" s="108"/>
+      <c r="H30" s="64"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="124"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="106"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="H31" s="66"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="125" t="s">
+      <c r="H31" s="64"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="125"/>
-      <c r="C32" s="125"/>
+      <c r="B32" s="123"/>
+      <c r="C32" s="123"/>
       <c r="D32" s="35">
         <f>SUM(D28:D30)</f>
         <v>0</v>
@@ -2135,68 +2195,68 @@
         <f>E32+F32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="66" t="str">
+      <c r="H32" s="64" t="str">
         <f>IF(D32=G32, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="126" t="s">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="84"/>
-      <c r="C33" s="84"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="54">
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="52">
         <f>D33*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F33" s="54">
+      <c r="F33" s="52">
         <f>D33*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H33" s="66"/>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="84" t="s">
+      <c r="H33" s="64"/>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="84"/>
-      <c r="C34" s="84"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="54">
+      <c r="B34" s="82"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="106"/>
+      <c r="E34" s="52">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F34" s="54">
+      <c r="F34" s="52">
         <f t="shared" ref="F34:F35" si="4">D34*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H34" s="66"/>
-    </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="126" t="s">
+      <c r="H34" s="64"/>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="54">
+      <c r="B35" s="82"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="106"/>
+      <c r="E35" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="54">
+      <c r="F35" s="52">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H35" s="66"/>
-    </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="125" t="s">
+      <c r="H35" s="64"/>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="125"/>
-      <c r="C36" s="125"/>
+      <c r="B36" s="123"/>
+      <c r="C36" s="123"/>
       <c r="D36" s="35">
         <f>SUM(D29:D35)</f>
         <v>0</v>
@@ -2205,45 +2265,45 @@
         <f t="shared" ref="E36" si="5">SUM(E29:E35)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="45">
+      <c r="F36" s="44">
         <f>E36*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H36" s="66"/>
-    </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="127"/>
-      <c r="B37" s="107"/>
-      <c r="C37" s="107"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="H37" s="66"/>
-    </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="127"/>
-      <c r="B38" s="107"/>
-      <c r="C38" s="107"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="H38" s="66"/>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="107"/>
-      <c r="B39" s="107"/>
-      <c r="C39" s="128"/>
-      <c r="D39" s="108"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="H39" s="66"/>
-    </row>
-    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="125" t="s">
+      <c r="H36" s="64"/>
+    </row>
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="125"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="H37" s="64"/>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="125"/>
+      <c r="B38" s="105"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="H38" s="64"/>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="105"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="126"/>
+      <c r="D39" s="106"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="H39" s="64"/>
+    </row>
+    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="125"/>
-      <c r="C40" s="125"/>
+      <c r="B40" s="123"/>
+      <c r="C40" s="123"/>
       <c r="D40" s="35"/>
       <c r="E40" s="38">
         <f>SUM(D37:D39)</f>
@@ -2253,1373 +2313,1431 @@
         <f>(D37)*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H40" s="66"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="126" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
+      <c r="H40" s="64"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="82"/>
+      <c r="C41" s="105"/>
       <c r="D41" s="39">
-        <v>110000</v>
-      </c>
-      <c r="E41" s="54">
-        <f>D41*91.91%</f>
-        <v>101100.99999999999</v>
-      </c>
-      <c r="F41" s="54">
-        <f>D41*8.09%</f>
-        <v>8899</v>
-      </c>
-      <c r="H41" s="66"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="126" t="s">
-        <v>128</v>
-      </c>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="39">
-        <v>514552.8</v>
-      </c>
-      <c r="E42" s="54">
-        <f>D42*91.91%</f>
-        <v>472925.47847999993</v>
-      </c>
-      <c r="F42" s="54">
-        <f>D42*8.09%</f>
-        <v>41627.321519999998</v>
-      </c>
-      <c r="H42" s="66"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="126" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="84"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="39">
-        <v>90000</v>
-      </c>
-      <c r="E43" s="54">
-        <f>D43*91.91%</f>
-        <v>82718.999999999985</v>
-      </c>
-      <c r="F43" s="54">
-        <f>D43*8.09%</f>
-        <v>7281</v>
-      </c>
-      <c r="H43" s="66"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="126" t="s">
-        <v>127</v>
-      </c>
-      <c r="B44" s="84"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="110">
-        <v>5842.51</v>
-      </c>
-      <c r="E44" s="54">
+        <f>50000+70000</f>
+        <v>120000</v>
+      </c>
+      <c r="E41" s="52">
+        <f>D41</f>
+        <v>120000</v>
+      </c>
+      <c r="F41" s="52"/>
+      <c r="H41" s="64"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="123" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="123"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="35">
+        <f>SUM(D41:D41)</f>
+        <v>120000</v>
+      </c>
+      <c r="E42" s="68">
+        <f>SUM(E41:E41)</f>
+        <v>120000</v>
+      </c>
+      <c r="F42" s="74">
+        <f>SUM(F41:F41)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="36">
+        <f>E42+F42</f>
+        <v>120000</v>
+      </c>
+      <c r="H42" s="64"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="82"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="28"/>
+      <c r="H43" s="64"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="124" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="82"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="39">
+        <v>6642</v>
+      </c>
+      <c r="E44" s="52">
         <f>D44*91.91%</f>
-        <v>5369.8509409999997</v>
-      </c>
-      <c r="F44" s="54">
+        <v>6104.6621999999998</v>
+      </c>
+      <c r="F44" s="52">
         <f>D44*8.09%</f>
-        <v>472.65905900000001</v>
-      </c>
-      <c r="H44" s="66"/>
-    </row>
-    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" s="125"/>
-      <c r="C45" s="125"/>
-      <c r="D45" s="35">
-        <f>SUM(D41:D44)</f>
-        <v>720395.31</v>
-      </c>
-      <c r="E45" s="70">
-        <f>SUM(E41:E44)</f>
-        <v>662115.32942099997</v>
-      </c>
-      <c r="F45" s="76">
-        <f>SUM(F41:F44)</f>
-        <v>58279.980578999995</v>
-      </c>
-      <c r="G45" s="36">
-        <f>E45+F45</f>
-        <v>720395.30999999994</v>
-      </c>
-      <c r="H45" s="66"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="126" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="84"/>
-      <c r="C46" s="84"/>
-      <c r="D46" s="110"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="28"/>
-      <c r="H46" s="66"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="126" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" s="84"/>
-      <c r="C47" s="107"/>
-      <c r="D47" s="39">
-        <v>6642</v>
-      </c>
-      <c r="E47" s="54">
-        <f>D47*91.91%</f>
-        <v>6104.6621999999998</v>
-      </c>
-      <c r="F47" s="54">
-        <f>D47*8.09%</f>
         <v>537.33780000000002</v>
       </c>
-      <c r="H47" s="66"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="126" t="s">
+      <c r="H44" s="64"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="84"/>
-      <c r="D48" s="147">
-        <f>142643.75+7840+70562</f>
-        <v>221045.75</v>
-      </c>
-      <c r="E48" s="54">
-        <f>D48*91.91%</f>
-        <v>203163.14882499998</v>
-      </c>
-      <c r="F48" s="54">
-        <f>D48*8.09%</f>
-        <v>17882.601175</v>
-      </c>
-      <c r="H48" s="66"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="126" t="s">
+      <c r="B45" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="82"/>
+      <c r="D45" s="39">
+        <f>142643.75+7840+70562.6</f>
+        <v>221046.35</v>
+      </c>
+      <c r="E45" s="52">
+        <f>D45*91.91%</f>
+        <v>203163.700285</v>
+      </c>
+      <c r="F45" s="52">
+        <f>D45*8.09%</f>
+        <v>17882.649715</v>
+      </c>
+      <c r="H45" s="64"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="124" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="107" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="84"/>
-      <c r="D49" s="147">
+      <c r="B46" s="105" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="82"/>
+      <c r="D46" s="39">
         <v>695037.24</v>
       </c>
-      <c r="E49" s="54">
-        <f>D49*91.91%</f>
+      <c r="E46" s="52">
+        <f>D46*91.91%</f>
         <v>638808.72728399991</v>
       </c>
-      <c r="F49" s="54">
-        <f>D49*8.09%</f>
+      <c r="F46" s="52">
+        <f>D46*8.09%</f>
         <v>56228.512715999997</v>
       </c>
-      <c r="H49" s="66"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="125" t="s">
+      <c r="H46" s="64"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="129"/>
-      <c r="C50" s="129"/>
-      <c r="D50" s="35">
-        <f>SUM(D47:D49)</f>
-        <v>922724.99</v>
-      </c>
-      <c r="E50" s="35">
-        <f t="shared" ref="E50:F50" si="6">SUM(E47:E49)</f>
-        <v>848076.53830899985</v>
-      </c>
-      <c r="F50" s="35">
+      <c r="B47" s="127"/>
+      <c r="C47" s="127"/>
+      <c r="D47" s="35">
+        <f>SUM(D44:D46)</f>
+        <v>922725.59</v>
+      </c>
+      <c r="E47" s="35">
+        <f t="shared" ref="E47:F47" si="6">SUM(E44:E46)</f>
+        <v>848077.08976899995</v>
+      </c>
+      <c r="F47" s="35">
         <f t="shared" si="6"/>
-        <v>74648.451690999995</v>
-      </c>
-      <c r="G50" s="36">
-        <f>E50+F50</f>
-        <v>922724.98999999987</v>
-      </c>
-      <c r="H50" s="66" t="str">
-        <f>IF(D50=G50, "", "Error")</f>
+        <v>74648.500230999998</v>
+      </c>
+      <c r="G47" s="36">
+        <f>E47+F47</f>
+        <v>922725.59</v>
+      </c>
+      <c r="H47" s="64" t="str">
+        <f>IF(D47=G47, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="84" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="84"/>
-      <c r="C51" s="84"/>
-      <c r="D51" s="110"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="4"/>
-      <c r="H51" s="66"/>
-    </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="130" t="s">
+      <c r="B48" s="82"/>
+      <c r="C48" s="82"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="4"/>
+      <c r="H48" s="64"/>
+    </row>
+    <row r="49" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="131"/>
-      <c r="C52" s="132"/>
-      <c r="D52" s="147">
+      <c r="B49" s="82"/>
+      <c r="C49" s="82"/>
+      <c r="D49" s="39">
         <v>434000</v>
       </c>
-      <c r="E52" s="65">
-        <f>D52</f>
+      <c r="E49" s="63">
+        <f>D49</f>
         <v>434000</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="36">
-        <f>D52</f>
+      <c r="F49" s="4"/>
+      <c r="G49" s="36">
+        <f>D49</f>
         <v>434000</v>
       </c>
-      <c r="H52" s="72">
-        <f>E52+F52</f>
+      <c r="H49" s="70">
+        <f>E49+F49</f>
         <v>434000</v>
       </c>
-      <c r="I52" s="81">
-        <f>H52-D52</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="81"/>
-    </row>
-    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="130" t="s">
+      <c r="I49" s="79">
+        <f>H49-D49</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="79"/>
+    </row>
+    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="131"/>
-      <c r="C53" s="132"/>
-      <c r="D53" s="147">
+      <c r="B50" s="82"/>
+      <c r="C50" s="82"/>
+      <c r="D50" s="39">
         <v>18000</v>
       </c>
-      <c r="E53" s="65"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="72"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-    </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="124" t="s">
+      <c r="E50" s="63">
+        <f>D50</f>
+        <v>18000</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="79"/>
+      <c r="J50" s="79"/>
+    </row>
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="133"/>
-      <c r="C54" s="84"/>
-      <c r="D54" s="39">
-        <v>0</v>
-      </c>
-      <c r="E54" s="65">
-        <f t="shared" ref="E54:E58" si="7">D54*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="54">
-        <f t="shared" ref="F54:F58" si="8">D54*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="36">
-        <f t="shared" ref="G54:G65" si="9">D54</f>
-        <v>0</v>
-      </c>
-      <c r="H54" s="72">
-        <f t="shared" ref="H54:H65" si="10">E54+F54</f>
-        <v>0</v>
-      </c>
-      <c r="I54" s="81"/>
-      <c r="J54" s="81"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="126" t="s">
-        <v>113</v>
-      </c>
-      <c r="B55" s="84"/>
-      <c r="C55" s="84"/>
-      <c r="D55" s="147">
+      <c r="B51" s="131"/>
+      <c r="C51" s="82"/>
+      <c r="D51" s="39">
+        <v>241100</v>
+      </c>
+      <c r="E51" s="63">
+        <f t="shared" ref="E51:E55" si="7">D51*91.91%</f>
+        <v>221595.00999999998</v>
+      </c>
+      <c r="F51" s="52">
+        <f t="shared" ref="F51:F55" si="8">D51*8.09%</f>
+        <v>19504.990000000002</v>
+      </c>
+      <c r="G51" s="36">
+        <f t="shared" ref="G51:G65" si="9">D51</f>
+        <v>241100</v>
+      </c>
+      <c r="H51" s="70">
+        <f t="shared" ref="H51:H65" si="10">E51+F51</f>
+        <v>241099.99999999997</v>
+      </c>
+      <c r="I51" s="79"/>
+      <c r="J51" s="79"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="124" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="82"/>
+      <c r="C52" s="82"/>
+      <c r="D52" s="39">
         <v>893616.94</v>
       </c>
-      <c r="E55" s="65">
+      <c r="E52" s="63">
         <f t="shared" si="7"/>
         <v>821323.32955399982</v>
       </c>
-      <c r="F55" s="54">
+      <c r="F52" s="52">
         <f t="shared" si="8"/>
         <v>72293.610445999991</v>
       </c>
+      <c r="G52" s="36">
+        <f t="shared" si="9"/>
+        <v>893616.94</v>
+      </c>
+      <c r="H52" s="70">
+        <f t="shared" si="10"/>
+        <v>893616.93999999983</v>
+      </c>
+      <c r="I52" s="79"/>
+      <c r="J52" s="79"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="124" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="82" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="82"/>
+      <c r="D53" s="39">
+        <v>129320</v>
+      </c>
+      <c r="E53" s="63">
+        <f>D53*91.91%</f>
+        <v>118858.01199999999</v>
+      </c>
+      <c r="F53" s="52">
+        <f t="shared" si="8"/>
+        <v>10461.987999999999</v>
+      </c>
+      <c r="G53" s="36">
+        <f t="shared" si="9"/>
+        <v>129320</v>
+      </c>
+      <c r="H53" s="70">
+        <f>E53+F53</f>
+        <v>129319.99999999999</v>
+      </c>
+      <c r="I53" s="79">
+        <f t="shared" ref="I53:I65" si="11">H53-D53</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="79">
+        <f t="shared" ref="J53:J65" si="12">G53-D53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="124" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="105" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" s="82"/>
+      <c r="D54" s="39">
+        <v>843680.39</v>
+      </c>
+      <c r="E54" s="63">
+        <f t="shared" si="7"/>
+        <v>775426.64644899999</v>
+      </c>
+      <c r="F54" s="52">
+        <f t="shared" si="8"/>
+        <v>68253.743551000007</v>
+      </c>
+      <c r="G54" s="36">
+        <f t="shared" si="9"/>
+        <v>843680.39</v>
+      </c>
+      <c r="H54" s="70">
+        <f t="shared" si="10"/>
+        <v>843680.39</v>
+      </c>
+      <c r="I54" s="79">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="79">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="125" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" s="105" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" s="105"/>
+      <c r="D55" s="39">
+        <v>897000</v>
+      </c>
+      <c r="E55" s="63">
+        <f t="shared" si="7"/>
+        <v>824432.7</v>
+      </c>
+      <c r="F55" s="52">
+        <f t="shared" si="8"/>
+        <v>72567.3</v>
+      </c>
       <c r="G55" s="36">
         <f t="shared" si="9"/>
-        <v>893616.94</v>
-      </c>
-      <c r="H55" s="72">
+        <v>897000</v>
+      </c>
+      <c r="H55" s="70">
         <f t="shared" si="10"/>
-        <v>893616.93999999983</v>
-      </c>
-      <c r="I55" s="81"/>
-      <c r="J55" s="81"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="126" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="84" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="84"/>
+        <v>897000</v>
+      </c>
+      <c r="I55" s="79">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="79">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="105" t="s">
+        <v>133</v>
+      </c>
+      <c r="B56" s="105"/>
+      <c r="C56" s="105"/>
       <c r="D56" s="39">
-        <v>129320</v>
-      </c>
-      <c r="E56" s="65">
-        <f>D56*91.91%</f>
-        <v>118858.01199999999</v>
-      </c>
-      <c r="F56" s="54">
-        <f t="shared" si="8"/>
-        <v>10461.987999999999</v>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="E56" s="63">
+        <f>D56</f>
+        <v>300000</v>
+      </c>
+      <c r="F56" s="52"/>
       <c r="G56" s="36">
         <f t="shared" si="9"/>
-        <v>129320</v>
-      </c>
-      <c r="H56" s="72">
-        <f>E56+F56</f>
-        <v>129319.99999999999</v>
-      </c>
-      <c r="I56" s="81">
-        <f t="shared" ref="I56:I65" si="11">H56-D56</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="81">
-        <f t="shared" ref="J56:J65" si="12">G56-D56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="126" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="107" t="s">
-        <v>121</v>
-      </c>
-      <c r="C57" s="84"/>
-      <c r="D57" s="147">
-        <v>843680.39</v>
-      </c>
-      <c r="E57" s="65">
-        <f t="shared" si="7"/>
-        <v>775426.64644899999</v>
-      </c>
-      <c r="F57" s="54">
-        <f t="shared" si="8"/>
-        <v>68253.743551000007</v>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="H56" s="70">
+        <f t="shared" si="10"/>
+        <v>300000</v>
+      </c>
+      <c r="I56" s="79"/>
+      <c r="J56" s="79"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="132" t="s">
+        <v>135</v>
+      </c>
+      <c r="B57" s="132"/>
+      <c r="C57" s="132"/>
+      <c r="D57" s="39">
+        <v>56600</v>
+      </c>
+      <c r="E57" s="63">
+        <f t="shared" ref="E57:E58" si="13">D57</f>
+        <v>56600</v>
+      </c>
+      <c r="F57" s="52"/>
       <c r="G57" s="36">
         <f t="shared" si="9"/>
-        <v>843680.39</v>
-      </c>
-      <c r="H57" s="72">
+        <v>56600</v>
+      </c>
+      <c r="H57" s="70">
         <f t="shared" si="10"/>
-        <v>843680.39</v>
-      </c>
-      <c r="I57" s="81">
+        <v>56600</v>
+      </c>
+      <c r="I57" s="79">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J57" s="81">
+      <c r="J57" s="79">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="127" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="107" t="s">
-        <v>125</v>
-      </c>
-      <c r="C58" s="107"/>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="132" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" s="203"/>
+      <c r="C58" s="204"/>
       <c r="D58" s="39">
-        <v>0</v>
-      </c>
-      <c r="E58" s="65">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="54">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+        <v>58200</v>
+      </c>
+      <c r="E58" s="63">
+        <f t="shared" si="13"/>
+        <v>58200</v>
+      </c>
+      <c r="F58" s="52"/>
       <c r="G58" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="72">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="81">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="81">
+        <v>58200</v>
+      </c>
+      <c r="H58" s="70"/>
+      <c r="I58" s="79"/>
+      <c r="J58" s="79">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="134" t="s">
-        <v>117</v>
-      </c>
-      <c r="B59" s="134"/>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="197" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="133"/>
       <c r="C59" s="134"/>
-      <c r="D59" s="147">
-        <v>56600</v>
-      </c>
-      <c r="E59" s="65">
-        <f t="shared" ref="E59" si="13">D59</f>
-        <v>56600</v>
-      </c>
-      <c r="F59" s="54"/>
+      <c r="D59" s="39">
+        <v>250000</v>
+      </c>
+      <c r="E59" s="63">
+        <f>D59</f>
+        <v>250000</v>
+      </c>
+      <c r="F59" s="52"/>
       <c r="G59" s="36">
         <f t="shared" si="9"/>
-        <v>56600</v>
-      </c>
-      <c r="H59" s="72">
+        <v>250000</v>
+      </c>
+      <c r="H59" s="70">
         <f t="shared" si="10"/>
-        <v>56600</v>
-      </c>
-      <c r="I59" s="81">
+        <v>250000</v>
+      </c>
+      <c r="I59" s="79">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J59" s="81">
+      <c r="J59" s="79">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="135" t="s">
-        <v>136</v>
-      </c>
-      <c r="B60" s="136"/>
-      <c r="C60" s="137"/>
-      <c r="D60" s="147">
-        <v>250000</v>
-      </c>
-      <c r="E60" s="65">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="197" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" s="133"/>
+      <c r="C60" s="134"/>
+      <c r="D60" s="39">
+        <v>330000</v>
+      </c>
+      <c r="E60" s="63">
         <f>D60</f>
-        <v>250000</v>
-      </c>
-      <c r="F60" s="54"/>
+        <v>330000</v>
+      </c>
+      <c r="F60" s="52"/>
       <c r="G60" s="36">
         <f t="shared" si="9"/>
-        <v>250000</v>
-      </c>
-      <c r="H60" s="72">
+        <v>330000</v>
+      </c>
+      <c r="H60" s="70">
         <f t="shared" si="10"/>
-        <v>250000</v>
-      </c>
-      <c r="I60" s="81">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="81">
+        <v>330000</v>
+      </c>
+      <c r="I60" s="79"/>
+      <c r="J60" s="79">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="176"/>
-      <c r="B61" s="177"/>
-      <c r="C61" s="178"/>
-      <c r="D61" s="147">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="206" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" s="207"/>
+      <c r="C61" s="208"/>
+      <c r="D61" s="39">
         <v>60000</v>
       </c>
-      <c r="E61" s="65">
-        <f t="shared" ref="E61" si="14">D61</f>
+      <c r="E61" s="63">
+        <f t="shared" ref="E61" si="14">D61*91.91%</f>
+        <v>55145.999999999993</v>
+      </c>
+      <c r="F61" s="52">
+        <f t="shared" ref="F61" si="15">D61*8.09%</f>
+        <v>4854</v>
+      </c>
+      <c r="G61" s="36">
+        <f t="shared" ref="G61" si="16">D61</f>
         <v>60000</v>
       </c>
-      <c r="F61" s="54"/>
-      <c r="G61" s="36">
-        <f t="shared" ref="G61" si="15">D61</f>
-        <v>60000</v>
-      </c>
-      <c r="H61" s="72">
-        <f t="shared" ref="H61" si="16">E61+F61</f>
-        <v>60000</v>
-      </c>
-      <c r="I61" s="81"/>
-      <c r="J61" s="81"/>
-    </row>
-    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="84" t="s">
+      <c r="H61" s="70">
+        <f t="shared" ref="H61" si="17">E61+F61</f>
+        <v>59999.999999999993</v>
+      </c>
+      <c r="I61" s="79"/>
+      <c r="J61" s="79"/>
+    </row>
+    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="B62" s="84"/>
-      <c r="C62" s="84"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
       <c r="D62" s="39">
-        <v>97935</v>
-      </c>
-      <c r="E62" s="65">
-        <f t="shared" ref="E62:E65" si="17">D62</f>
-        <v>97935</v>
-      </c>
-      <c r="F62" s="54"/>
+        <v>10775</v>
+      </c>
+      <c r="E62" s="63">
+        <f t="shared" ref="E62:E65" si="18">D62</f>
+        <v>10775</v>
+      </c>
+      <c r="F62" s="52"/>
       <c r="G62" s="36">
         <f t="shared" si="9"/>
-        <v>97935</v>
-      </c>
-      <c r="H62" s="72">
+        <v>10775</v>
+      </c>
+      <c r="H62" s="70">
         <f t="shared" si="10"/>
-        <v>97935</v>
-      </c>
-      <c r="I62" s="81">
+        <v>10775</v>
+      </c>
+      <c r="I62" s="79">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J62" s="81">
+      <c r="J62" s="79">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="148" t="s">
-        <v>138</v>
-      </c>
-      <c r="B63" s="131"/>
-      <c r="C63" s="132"/>
-      <c r="D63" s="147">
-        <v>21900</v>
-      </c>
-      <c r="E63" s="65">
-        <f t="shared" si="17"/>
-        <v>21900</v>
-      </c>
-      <c r="F63" s="54"/>
+    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="144" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="129"/>
+      <c r="C63" s="130"/>
+      <c r="D63" s="39">
+        <v>107437.59</v>
+      </c>
+      <c r="E63" s="63">
+        <f t="shared" si="18"/>
+        <v>107437.59</v>
+      </c>
+      <c r="F63" s="52"/>
       <c r="G63" s="36">
         <f t="shared" si="9"/>
+        <v>107437.59</v>
+      </c>
+      <c r="H63" s="70">
+        <f t="shared" si="10"/>
+        <v>107437.59</v>
+      </c>
+      <c r="I63" s="79">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="79">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="129"/>
+      <c r="C64" s="201"/>
+      <c r="D64" s="39">
         <v>21900</v>
       </c>
-      <c r="H63" s="72">
+      <c r="E64" s="63">
+        <f t="shared" si="18"/>
+        <v>21900</v>
+      </c>
+      <c r="F64" s="52"/>
+      <c r="G64" s="36">
+        <f t="shared" si="9"/>
+        <v>21900</v>
+      </c>
+      <c r="H64" s="70">
         <f t="shared" si="10"/>
         <v>21900</v>
       </c>
-      <c r="I63" s="81">
+      <c r="I64" s="79">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J63" s="81">
+      <c r="J64" s="79">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="148"/>
-      <c r="B64" s="131"/>
-      <c r="C64" s="132"/>
-      <c r="D64" s="147">
-        <v>107437.59</v>
-      </c>
-      <c r="E64" s="65">
-        <f t="shared" si="17"/>
-        <v>107437.59</v>
-      </c>
-      <c r="F64" s="54"/>
-      <c r="G64" s="36">
-        <f t="shared" si="9"/>
-        <v>107437.59</v>
-      </c>
-      <c r="H64" s="72">
-        <f t="shared" si="10"/>
-        <v>107437.59</v>
-      </c>
-      <c r="I64" s="81">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="81">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="173" t="s">
-        <v>137</v>
-      </c>
-      <c r="B65" s="174"/>
-      <c r="C65" s="175"/>
-      <c r="D65" s="147">
+    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="198" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="199"/>
+      <c r="C65" s="200"/>
+      <c r="D65" s="39">
         <v>220000</v>
       </c>
-      <c r="E65" s="65">
-        <f t="shared" si="17"/>
+      <c r="E65" s="63">
+        <f t="shared" si="18"/>
         <v>220000</v>
       </c>
-      <c r="F65" s="54"/>
+      <c r="F65" s="52"/>
       <c r="G65" s="36">
         <f t="shared" si="9"/>
         <v>220000</v>
       </c>
-      <c r="H65" s="72">
+      <c r="H65" s="70">
         <f t="shared" si="10"/>
         <v>220000</v>
       </c>
-      <c r="I65" s="81">
+      <c r="I65" s="79">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J65" s="81">
+      <c r="J65" s="79">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="125" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="129"/>
-      <c r="C66" s="129"/>
+      <c r="B66" s="127"/>
+      <c r="C66" s="127"/>
       <c r="D66" s="35">
-        <f>SUM(D52:D65)</f>
-        <v>3132489.92</v>
+        <f>SUM(D49:D65)</f>
+        <v>4871629.92</v>
       </c>
       <c r="E66" s="35">
-        <f>SUM(E52:E65)</f>
-        <v>2963480.578003</v>
+        <f>SUM(E49:E65)</f>
+        <v>4623694.2880029995</v>
       </c>
       <c r="F66" s="35">
-        <f>SUM(F52:F65)</f>
-        <v>151009.34199699998</v>
+        <f>SUM(F49:F65)</f>
+        <v>247935.63199700002</v>
       </c>
       <c r="G66" s="36">
         <f>E66+F66</f>
-        <v>3114489.92</v>
-      </c>
-      <c r="H66" s="66" t="str">
+        <v>4871629.92</v>
+      </c>
+      <c r="H66" s="64" t="str">
         <f>IF(D66=G66, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I66" s="81">
+        <v/>
+      </c>
+      <c r="I66" s="79">
         <f>D66-G66</f>
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="84"/>
-      <c r="B67" s="84"/>
-      <c r="C67" s="84"/>
-      <c r="D67" s="110"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="82"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="82"/>
+      <c r="D67" s="108"/>
       <c r="E67" s="41"/>
       <c r="F67" s="4"/>
-      <c r="H67" s="66"/>
-    </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="84"/>
-      <c r="B68" s="84"/>
-      <c r="C68" s="84"/>
-      <c r="D68" s="110"/>
+      <c r="H67" s="64"/>
+    </row>
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="82"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="108"/>
       <c r="E68" s="40"/>
       <c r="F68" s="4"/>
-      <c r="H68" s="66"/>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="84"/>
-      <c r="B69" s="84"/>
-      <c r="C69" s="84"/>
-      <c r="D69" s="110"/>
+      <c r="H68" s="64"/>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="82"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="108"/>
       <c r="E69" s="40"/>
       <c r="F69" s="4"/>
-      <c r="H69" s="66"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="127" t="s">
-        <v>110</v>
-      </c>
-      <c r="B70" s="107"/>
-      <c r="C70" s="84"/>
-      <c r="D70" s="147">
+      <c r="H69" s="64"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="125" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="105"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="39">
         <v>82100</v>
       </c>
-      <c r="E70" s="65">
+      <c r="E70" s="63">
         <f>D70*91.91%</f>
         <v>75458.109999999986</v>
       </c>
-      <c r="F70" s="54">
+      <c r="F70" s="52">
         <f>D70*8.09%</f>
         <v>6641.89</v>
       </c>
-      <c r="G70" s="71"/>
-      <c r="H70" s="66"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="179" t="s">
-        <v>126</v>
-      </c>
-      <c r="B71" s="180"/>
-      <c r="C71" s="181"/>
-      <c r="D71" s="147">
+      <c r="G70" s="69"/>
+      <c r="H70" s="64"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="125" t="s">
+        <v>146</v>
+      </c>
+      <c r="B71" s="202"/>
+      <c r="C71" s="130"/>
+      <c r="D71" s="39">
+        <v>20900</v>
+      </c>
+      <c r="E71" s="63">
+        <f>D71*91.91%</f>
+        <v>19209.189999999999</v>
+      </c>
+      <c r="F71" s="52">
+        <f>D71*8.09%</f>
+        <v>1690.81</v>
+      </c>
+      <c r="G71" s="69"/>
+      <c r="H71" s="64"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="169" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="170"/>
+      <c r="C72" s="171"/>
+      <c r="D72" s="39">
         <v>229300</v>
       </c>
-      <c r="E71" s="65">
-        <f t="shared" ref="E71:E72" si="18">D71</f>
+      <c r="E72" s="63">
+        <f t="shared" ref="E72:E73" si="19">D72</f>
         <v>229300</v>
       </c>
-      <c r="F71" s="54"/>
-      <c r="G71" s="71"/>
-      <c r="H71" s="66"/>
-    </row>
-    <row r="72" spans="1:10" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="179" t="s">
-        <v>126</v>
-      </c>
-      <c r="B72" s="180"/>
-      <c r="C72" s="181"/>
-      <c r="D72" s="147">
+      <c r="F72" s="52"/>
+      <c r="G72" s="69"/>
+      <c r="H72" s="64"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="169" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="170"/>
+      <c r="C73" s="171"/>
+      <c r="D73" s="39">
         <v>227600</v>
       </c>
-      <c r="E72" s="65">
-        <f t="shared" si="18"/>
+      <c r="E73" s="63">
+        <f t="shared" si="19"/>
         <v>227600</v>
       </c>
-      <c r="F72" s="54"/>
-      <c r="H72" s="66"/>
-      <c r="I72" s="36"/>
-    </row>
-    <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="125" t="s">
+      <c r="F73" s="52"/>
+      <c r="H73" s="64"/>
+      <c r="I73" s="36"/>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="125"/>
-      <c r="C73" s="125"/>
-      <c r="D73" s="35">
-        <f>SUM(D70:D72)</f>
-        <v>539000</v>
-      </c>
-      <c r="E73" s="35">
-        <f>SUM(E70:E72)</f>
-        <v>532358.11</v>
-      </c>
-      <c r="F73" s="35">
-        <f>SUM(F70:F72)</f>
-        <v>6641.89</v>
-      </c>
-      <c r="G73" s="36">
-        <f>E73+F73</f>
-        <v>539000</v>
-      </c>
-      <c r="H73" s="66" t="str">
-        <f>IF(D73=G73, "", "Error")</f>
+      <c r="B74" s="123"/>
+      <c r="C74" s="123"/>
+      <c r="D74" s="35">
+        <f>SUM(D70:D73)</f>
+        <v>559900</v>
+      </c>
+      <c r="E74" s="35">
+        <f>SUM(E70:E73)</f>
+        <v>551567.30000000005</v>
+      </c>
+      <c r="F74" s="35">
+        <f>SUM(F70:F73)</f>
+        <v>8332.7000000000007</v>
+      </c>
+      <c r="G74" s="36">
+        <f>E74+F74</f>
+        <v>559900</v>
+      </c>
+      <c r="H74" s="64" t="str">
+        <f>IF(D74=G74, "", "Error")</f>
         <v/>
       </c>
-      <c r="J73" s="36"/>
-    </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="84"/>
-      <c r="B74" s="84"/>
-      <c r="C74" s="84"/>
-      <c r="D74" s="110"/>
-      <c r="E74" s="41"/>
-      <c r="F74" s="4"/>
-      <c r="H74" s="66"/>
-    </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="84"/>
-      <c r="B75" s="84"/>
-      <c r="C75" s="84"/>
-      <c r="D75" s="110"/>
-      <c r="E75" s="40"/>
+      <c r="J74" s="36"/>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="82"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="108"/>
+      <c r="E75" s="41"/>
       <c r="F75" s="4"/>
-      <c r="H75" s="66"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="126" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76" s="84"/>
-      <c r="C76" s="84"/>
-      <c r="D76" s="110"/>
+      <c r="H75" s="64"/>
+    </row>
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="82"/>
+      <c r="B76" s="82"/>
+      <c r="C76" s="82"/>
+      <c r="D76" s="108"/>
       <c r="E76" s="40"/>
       <c r="F76" s="4"/>
-      <c r="H76" s="66"/>
-    </row>
-    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="126" t="s">
+      <c r="H76" s="64"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="124" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" s="82"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="108"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="4"/>
+      <c r="H77" s="64"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="124" t="s">
         <v>14</v>
       </c>
-      <c r="B77" s="84" t="s">
+      <c r="B78" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="C77" s="84"/>
-      <c r="D77" s="39">
-        <v>285700</v>
-      </c>
-      <c r="E77" s="65">
-        <f>D77*91.91%</f>
-        <v>262586.87</v>
-      </c>
-      <c r="F77" s="54">
-        <f>D77*8.09%</f>
-        <v>23113.13</v>
-      </c>
-      <c r="G77" t="s">
-        <v>118</v>
-      </c>
-      <c r="H77" s="66"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="126" t="s">
+      <c r="C78" s="82" t="s">
+        <v>145</v>
+      </c>
+      <c r="D78" s="39"/>
+      <c r="E78" s="63">
+        <f>D78*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="52">
+        <f>D78*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>116</v>
+      </c>
+      <c r="H78" s="64"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="84"/>
-      <c r="C78" s="84"/>
-      <c r="D78" s="39">
+      <c r="B79" s="82"/>
+      <c r="C79" s="82"/>
+      <c r="D79" s="39">
         <v>45000</v>
       </c>
-      <c r="E78" s="65">
-        <f>D78*91.91%</f>
+      <c r="E79" s="63">
+        <f>D79*91.91%</f>
         <v>41359.499999999993</v>
       </c>
-      <c r="F78" s="54">
-        <f>D78*8.09%</f>
+      <c r="F79" s="52">
+        <f>D79*8.09%</f>
         <v>3640.5</v>
       </c>
-      <c r="H78" s="66"/>
-      <c r="J78" s="39"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="84"/>
-      <c r="B79" s="84"/>
-      <c r="C79" s="84"/>
-      <c r="D79" s="110"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="4"/>
-      <c r="H79" s="66"/>
-      <c r="J79" s="36"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="125"/>
-      <c r="B80" s="125"/>
-      <c r="C80" s="125"/>
-      <c r="D80" s="35">
-        <f>SUM(D77:D79)</f>
-        <v>330700</v>
-      </c>
-      <c r="E80" s="35">
-        <f>SUM(E77:E79)</f>
-        <v>303946.37</v>
-      </c>
-      <c r="F80" s="35">
-        <f>SUM(F77:F79)</f>
-        <v>26753.63</v>
-      </c>
-      <c r="G80" s="36">
-        <f>E80+F80</f>
-        <v>330700</v>
-      </c>
-      <c r="H80" s="66" t="str">
-        <f>IF(D80=G80, "", "Error")</f>
+      <c r="H79" s="64"/>
+      <c r="J79" s="39"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="124" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" s="82"/>
+      <c r="C80" s="82"/>
+      <c r="D80" s="108">
+        <v>150000</v>
+      </c>
+      <c r="E80" s="63">
+        <f>D80*91.91%</f>
+        <v>137865</v>
+      </c>
+      <c r="F80" s="52">
+        <f>D80*8.09%</f>
+        <v>12135</v>
+      </c>
+      <c r="H80" s="64"/>
+      <c r="J80" s="36"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="123"/>
+      <c r="B81" s="123"/>
+      <c r="C81" s="123"/>
+      <c r="D81" s="35">
+        <f>SUM(D78:D80)</f>
+        <v>195000</v>
+      </c>
+      <c r="E81" s="35">
+        <f>SUM(E78:E80)</f>
+        <v>179224.5</v>
+      </c>
+      <c r="F81" s="35">
+        <f>SUM(F78:F80)</f>
+        <v>15775.5</v>
+      </c>
+      <c r="G81" s="36">
+        <f>E81+F81</f>
+        <v>195000</v>
+      </c>
+      <c r="H81" s="64" t="str">
+        <f>IF(D81=G81, "", "Error")</f>
         <v/>
       </c>
-      <c r="J80" s="36"/>
-    </row>
-    <row r="81" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="126" t="s">
+      <c r="J81" s="36"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="B81" s="84"/>
-      <c r="C81" s="84"/>
-      <c r="D81" s="39"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="4"/>
-      <c r="H81" s="66"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" s="126" t="s">
+      <c r="B82" s="82"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="4"/>
+      <c r="H82" s="64"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="B82" s="84"/>
-      <c r="C82" s="84"/>
-      <c r="D82" s="39">
-        <v>100705.49</v>
-      </c>
-      <c r="E82" s="65">
-        <f>D82*91.91%</f>
-        <v>92558.415859000001</v>
-      </c>
-      <c r="F82" s="54">
-        <f>D82*8.09%</f>
-        <v>8147.0741410000001</v>
-      </c>
-      <c r="H82" s="66"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="126" t="s">
+      <c r="B83" s="82"/>
+      <c r="C83" s="82"/>
+      <c r="D83" s="39">
+        <v>153381.85</v>
+      </c>
+      <c r="E83" s="63">
+        <f>D83*91.91%</f>
+        <v>140973.25833499999</v>
+      </c>
+      <c r="F83" s="52">
+        <f>D83*8.09%</f>
+        <v>12408.591665</v>
+      </c>
+      <c r="H83" s="64"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="124" t="s">
         <v>75</v>
       </c>
-      <c r="B83" s="84"/>
-      <c r="C83" s="138"/>
-      <c r="D83" s="39">
+      <c r="B84" s="82"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="39">
         <v>57500</v>
       </c>
-      <c r="E83" s="65">
-        <f>D83*91.91%</f>
+      <c r="E84" s="63">
+        <f>D84*91.91%</f>
         <v>52848.249999999993</v>
       </c>
-      <c r="F83" s="54">
-        <f>D83*8.09%</f>
+      <c r="F84" s="52">
+        <f>D84*8.09%</f>
         <v>4651.75</v>
       </c>
-      <c r="H83" s="66"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" s="125" t="s">
+      <c r="H84" s="64"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="B84" s="125"/>
-      <c r="C84" s="125"/>
-      <c r="D84" s="69">
-        <f>SUM(D82:D83)</f>
-        <v>158205.49</v>
-      </c>
-      <c r="E84" s="63">
-        <f t="shared" ref="E84:F84" si="19">SUM(E82:E83)</f>
-        <v>145406.665859</v>
-      </c>
-      <c r="F84" s="63">
-        <f t="shared" si="19"/>
-        <v>12798.824141000001</v>
-      </c>
-      <c r="G84" s="36">
-        <f>E84+F84</f>
-        <v>158205.49</v>
-      </c>
-      <c r="H84" s="66" t="str">
-        <f>IF(D84=G84, "", "Error")</f>
+      <c r="B85" s="123"/>
+      <c r="C85" s="123"/>
+      <c r="D85" s="67">
+        <f>SUM(D83:D84)</f>
+        <v>210881.85</v>
+      </c>
+      <c r="E85" s="61">
+        <f t="shared" ref="E85:F85" si="20">SUM(E83:E84)</f>
+        <v>193821.50833499999</v>
+      </c>
+      <c r="F85" s="61">
+        <f t="shared" si="20"/>
+        <v>17060.341665</v>
+      </c>
+      <c r="G85" s="36">
+        <f>E85+F85</f>
+        <v>210881.84999999998</v>
+      </c>
+      <c r="H85" s="64" t="str">
+        <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="84"/>
-      <c r="B85" s="84"/>
-      <c r="C85" s="84"/>
-      <c r="D85" s="84"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="4"/>
-      <c r="H85" s="66"/>
-    </row>
-    <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="139" t="s">
+    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="82"/>
+      <c r="B86" s="82"/>
+      <c r="C86" s="82"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="4"/>
+      <c r="H86" s="64"/>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="B86" s="139"/>
-      <c r="C86" s="139"/>
-      <c r="D86" s="85">
-        <f>8500000-5559993.91</f>
-        <v>2940006.09</v>
-      </c>
-      <c r="E86" s="44">
-        <f>D86*91.91%</f>
-        <v>2702159.5973189995</v>
-      </c>
-      <c r="F86" s="56">
-        <f>D86*8.09%</f>
-        <v>237846.49268099997</v>
-      </c>
-      <c r="G86" s="36">
-        <f>E86+F86</f>
-        <v>2940006.0899999994</v>
-      </c>
-      <c r="H86" s="66" t="str">
-        <f>IF(D86=G86, "", "Error")</f>
+      <c r="B87" s="136"/>
+      <c r="C87" s="136"/>
+      <c r="D87" s="83"/>
+      <c r="E87" s="43">
+        <f>D87*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F87" s="54">
+        <f>D87*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G87" s="36">
+        <f>E87+F87</f>
+        <v>0</v>
+      </c>
+      <c r="H87" s="64" t="str">
+        <f>IF(D87=G87, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="140"/>
-      <c r="B87" s="83"/>
-      <c r="C87" s="83"/>
-      <c r="D87" s="83"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="66"/>
-    </row>
-    <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="141" t="s">
+    <row r="88" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="137"/>
+      <c r="B88" s="81"/>
+      <c r="C88" s="81"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="66"/>
+      <c r="H88" s="64"/>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="138" t="s">
         <v>76</v>
       </c>
-      <c r="B88" s="142"/>
-      <c r="C88" s="143"/>
-      <c r="D88" s="86">
-        <f>SUM(D86+D84+D80+D73+D66+D50+D32+D27+D45)</f>
-        <v>9970527.8000000007</v>
-      </c>
-      <c r="E88" s="64">
-        <f>SUM(E86+E84+E80+E73+E66+E50+E32+E27+E45)</f>
-        <v>9285284.4035109989</v>
-      </c>
-      <c r="F88" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="G88" s="36" t="e">
-        <f>E88+F88</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H88" s="66" t="e">
-        <f>IF(D88=G88, "", "Error")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I88" s="81" t="e">
-        <f>D88-G88</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="83"/>
-      <c r="B89" s="83"/>
-      <c r="C89" s="83"/>
-      <c r="D89" s="83"/>
-      <c r="E89" s="36"/>
-    </row>
-    <row r="90" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="144" t="s">
-        <v>112</v>
-      </c>
-      <c r="B90" s="145"/>
-      <c r="C90" s="145"/>
-      <c r="D90" s="83"/>
+      <c r="B89" s="139"/>
+      <c r="C89" s="140"/>
+      <c r="D89" s="84">
+        <f>SUM(D87+D85+D81+D74+D66+D47+D32+D27+D42)</f>
+        <v>8097597.3599999994</v>
+      </c>
+      <c r="E89" s="62">
+        <f>SUM(E87+E85+E81+E74+E66+E47+E32+E27+E42)</f>
+        <v>7635352.1721069999</v>
+      </c>
+      <c r="F89" s="62">
+        <f>SUM(F27+F42+F47+F66+F74+F81+F85+F87)</f>
+        <v>462245.18789300008</v>
+      </c>
+      <c r="G89" s="36">
+        <f>E89+F89</f>
+        <v>8097597.3600000003</v>
+      </c>
+      <c r="H89" s="64" t="str">
+        <f>IF(D89=G89, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I89" s="79">
+        <f>D89-G89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="81"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="81"/>
+      <c r="D90" s="81"/>
       <c r="E90" s="36"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="C91" s="59"/>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="141" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91" s="142"/>
+      <c r="C91" s="142"/>
+      <c r="D91" s="81"/>
       <c r="E91" s="36"/>
     </row>
-    <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="C92" s="59"/>
+      <c r="C92" s="57"/>
       <c r="E92" s="36"/>
     </row>
-    <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="61" t="s">
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="C93" s="57"/>
+      <c r="E93" s="36"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B93" s="62"/>
-      <c r="C93" s="60">
-        <f>SUM(C91:C92)</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="36"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B94" s="60"/>
+      <c r="C94" s="58">
+        <f>SUM(C92:C93)</f>
+        <v>0</v>
+      </c>
       <c r="E94" s="36"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E95" s="57"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="168" t="s">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E96" s="55"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="164" t="s">
         <v>86</v>
       </c>
-      <c r="B96" s="169"/>
-      <c r="C96" s="169"/>
-      <c r="D96" s="169"/>
-      <c r="E96" s="78" t="s">
+      <c r="B97" s="165"/>
+      <c r="C97" s="165"/>
+      <c r="D97" s="165"/>
+      <c r="E97" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="F96" s="79" t="s">
+      <c r="F97" s="77" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="165"/>
-      <c r="B97" s="166"/>
-      <c r="C97" s="167"/>
-      <c r="D97" s="39"/>
-      <c r="E97" s="65">
-        <f t="shared" ref="E97:E98" si="20">D97*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F97" s="54">
-        <f t="shared" ref="F97:F98" si="21">D97*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="170"/>
-      <c r="B98" s="171"/>
-      <c r="C98" s="172"/>
+    <row r="98" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="161"/>
+      <c r="B98" s="162"/>
+      <c r="C98" s="163"/>
       <c r="D98" s="39"/>
-      <c r="E98" s="65">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="F98" s="54">
+      <c r="E98" s="63">
+        <f t="shared" ref="E98:E99" si="21">D98*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="52">
+        <f t="shared" ref="F98:F99" si="22">D98*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="166"/>
+      <c r="B99" s="167"/>
+      <c r="C99" s="168"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="63">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" s="162" t="s">
+      <c r="F99" s="52">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="B99" s="163"/>
-      <c r="C99" s="164"/>
-      <c r="D99" s="77">
-        <f>SUM(D97:D98)</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="77">
-        <f>SUM(E97:E98)</f>
-        <v>0</v>
-      </c>
-      <c r="F99" s="77">
-        <f>SUM(F97:F98)</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="36">
-        <f>E99+F99</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="66" t="str">
-        <f>IF(D99=H99, "", "Error")</f>
+      <c r="B100" s="159"/>
+      <c r="C100" s="160"/>
+      <c r="D100" s="75">
+        <f>SUM(D98:D99)</f>
+        <v>0</v>
+      </c>
+      <c r="E100" s="75">
+        <f>SUM(E98:E99)</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="75">
+        <f>SUM(F98:F99)</f>
+        <v>0</v>
+      </c>
+      <c r="H100" s="36">
+        <f>E100+F100</f>
+        <v>0</v>
+      </c>
+      <c r="I100" s="64" t="str">
+        <f>IF(D100=H100, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E101" s="36"/>
-    </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="30" t="s">
+    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E102" s="36"/>
+    </row>
+    <row r="103" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="B102" s="31">
-        <f>D88</f>
-        <v>9970527.8000000007</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="32" t="s">
+      <c r="B103" s="31">
+        <f>D89</f>
+        <v>8097597.3599999994</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="B103" s="33">
-        <f>D88-D86</f>
-        <v>7030521.7100000009</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D104" s="152"/>
-      <c r="E104" s="152"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="11" t="s">
+      <c r="B104" s="33">
+        <f>D89-D87</f>
+        <v>8097597.3599999994</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D105" s="148"/>
+      <c r="E105" s="148"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B105" s="12"/>
-      <c r="C105" s="13"/>
-      <c r="D105" s="152"/>
-      <c r="E105" s="152"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="14" t="s">
+      <c r="B106" s="12"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="148"/>
+      <c r="E106" s="148"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B106" s="7">
-        <v>4069066.0394519484</v>
-      </c>
-      <c r="C106" s="15"/>
-      <c r="D106" s="152"/>
-      <c r="E106" s="152"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="16" t="s">
+      <c r="B107" s="7">
+        <v>5892489.5763089471</v>
+      </c>
+      <c r="C107" s="15"/>
+      <c r="D107" s="148"/>
+      <c r="E107" s="148"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B107" s="25">
+      <c r="B108" s="25">
         <f>PRORRATEO!G52</f>
-        <v>7423417.4468569998</v>
-      </c>
-      <c r="C107" s="15" t="s">
+        <v>12695174.355166664</v>
+      </c>
+      <c r="C108" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D107" s="152"/>
-      <c r="E107" s="152"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="16" t="s">
+      <c r="D108" s="148"/>
+      <c r="E108" s="148"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B108" s="80">
-        <f>-B103</f>
-        <v>-7030521.7100000009</v>
-      </c>
-      <c r="C108" s="13"/>
-      <c r="D108" s="152"/>
-      <c r="E108" s="152"/>
-      <c r="G108" s="39"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="16" t="s">
+      <c r="B109" s="78">
+        <f>-B104</f>
+        <v>-8097597.3599999994</v>
+      </c>
+      <c r="C109" s="13"/>
+      <c r="D109" s="148"/>
+      <c r="E109" s="148"/>
+      <c r="G109" s="39"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B109" s="80">
-        <f>-D99</f>
-        <v>0</v>
-      </c>
-      <c r="C109" s="13"/>
-      <c r="D109" s="152"/>
-      <c r="E109" s="152"/>
-      <c r="G109" s="47"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="16" t="s">
+      <c r="B110" s="78">
+        <f>-D100</f>
+        <v>0</v>
+      </c>
+      <c r="C110" s="13"/>
+      <c r="D110" s="148"/>
+      <c r="E110" s="148"/>
+      <c r="G110" s="46"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B110" s="80">
-        <f>-B116</f>
-        <v>-40000</v>
-      </c>
-      <c r="C110" s="17"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="16" t="s">
+      <c r="B111" s="78">
+        <f>-B117</f>
+        <v>-20000</v>
+      </c>
+      <c r="C111" s="17"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B111" s="26">
-        <f>-C93</f>
-        <v>0</v>
-      </c>
-      <c r="C111" s="17"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="14" t="s">
+      <c r="B112" s="26">
+        <f>-C94</f>
+        <v>0</v>
+      </c>
+      <c r="C112" s="17"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B112" s="18">
-        <f>SUM(B106:B111)</f>
-        <v>4421961.7763089463</v>
-      </c>
-      <c r="C112" s="67"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="17"/>
-      <c r="C113" s="13"/>
-      <c r="D113" s="20"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B113" s="18">
+        <f>SUM(B107:B112)</f>
+        <v>10470066.57147561</v>
+      </c>
+      <c r="C113" s="65"/>
+      <c r="D113" s="36"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="17"/>
       <c r="C114" s="13"/>
-      <c r="D114" s="36"/>
-      <c r="E114" s="81"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="11" t="s">
+      <c r="D114" s="20"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C115" s="13"/>
+      <c r="D115" s="36"/>
+      <c r="E115" s="79"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B115" s="92">
-        <v>-162694.54000000004</v>
-      </c>
-      <c r="C115" s="19"/>
-      <c r="D115" s="81"/>
-      <c r="E115" s="81"/>
-      <c r="F115" s="81"/>
-    </row>
-    <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B116" s="26">
-        <v>40000</v>
+      <c r="B116" s="90">
+        <v>-122694.54000000004</v>
       </c>
       <c r="C116" s="19"/>
-      <c r="D116" s="81"/>
-      <c r="E116" s="87"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="14"/>
-      <c r="B117" s="80"/>
+      <c r="D116" s="79"/>
+      <c r="E116" s="79"/>
+      <c r="F116" s="79"/>
+    </row>
+    <row r="117" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B117" s="26">
+        <v>20000</v>
+      </c>
       <c r="C117" s="19"/>
-      <c r="E117" s="36"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D117" s="79"/>
+      <c r="E117" s="85"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="14"/>
-      <c r="B118" s="80"/>
+      <c r="B118" s="78"/>
       <c r="C118" s="19"/>
-      <c r="D118" s="146"/>
       <c r="E118" s="36"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="28" t="s">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="14"/>
+      <c r="B119" s="78"/>
+      <c r="C119" s="19"/>
+      <c r="D119" s="143"/>
+      <c r="E119" s="36"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B119" s="29">
-        <f>SUM(B115:B118)</f>
-        <v>-122694.54000000004</v>
-      </c>
-      <c r="C119" s="19"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C120" s="20"/>
-      <c r="D120" s="81"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B121" s="17"/>
-      <c r="C121" s="13"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N123" s="8"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B126" s="151"/>
-      <c r="C126" s="151"/>
-      <c r="D126" s="151"/>
-      <c r="E126" s="151"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B127" s="151"/>
-      <c r="C127" s="151"/>
-      <c r="D127" s="151"/>
-      <c r="E127" s="151"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B128" s="151"/>
-      <c r="C128" s="151"/>
-      <c r="D128" s="151"/>
-      <c r="E128" s="151"/>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B129" s="151"/>
-      <c r="C129" s="151"/>
-      <c r="D129" s="151"/>
-      <c r="E129" s="151"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B130" s="151"/>
-      <c r="C130" s="151"/>
-      <c r="D130" s="151"/>
-      <c r="E130" s="151"/>
+      <c r="B120" s="29">
+        <f>SUM(B116:B119)</f>
+        <v>-102694.54000000004</v>
+      </c>
+      <c r="C120" s="19"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C121" s="20"/>
+      <c r="D121" s="79"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B122" s="17"/>
+      <c r="C122" s="13"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N124" s="8"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B127" s="147"/>
+      <c r="C127" s="147"/>
+      <c r="D127" s="147"/>
+      <c r="E127" s="147"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B128" s="147"/>
+      <c r="C128" s="147"/>
+      <c r="D128" s="147"/>
+      <c r="E128" s="147"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" s="147"/>
+      <c r="C129" s="147"/>
+      <c r="D129" s="147"/>
+      <c r="E129" s="147"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" s="147"/>
+      <c r="C130" s="147"/>
+      <c r="D130" s="147"/>
+      <c r="E130" s="147"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" s="147"/>
+      <c r="C131" s="147"/>
+      <c r="D131" s="147"/>
+      <c r="E131" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B126:E130"/>
-    <mergeCell ref="D104:E109"/>
+    <mergeCell ref="B127:E131"/>
+    <mergeCell ref="D105:E110"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A97:D97"/>
     <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A98:C98"/>
     <mergeCell ref="A65:C65"/>
     <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A71:C71"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3630,185 +3748,183 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="193" t="str">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="184" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 17/04</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="96" t="s">
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="186"/>
+      <c r="K1" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="L1" s="182">
-        <f>RESUMEN!D88</f>
-        <v>9970527.8000000007</v>
-      </c>
-      <c r="M1" s="183"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="55">
+      <c r="L1" s="173">
+        <f>RESUMEN!D89</f>
+        <v>8097597.3599999994</v>
+      </c>
+      <c r="M1" s="174"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="53">
         <f>L1*8.09%</f>
-        <v>806615.69902000006</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="196"/>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="98" t="s">
+        <v>655095.6264239999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="187"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="189"/>
+      <c r="K2" s="96" t="s">
         <v>97</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="99">
+      <c r="M2" s="97">
         <v>8500000</v>
       </c>
-      <c r="N2" s="100"/>
-      <c r="O2" s="55">
+      <c r="N2" s="98"/>
+      <c r="O2" s="53">
         <f>O1-K7-553-50-86-8</f>
-        <v>191016.81052000017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="197"/>
-      <c r="I3" s="197"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="98" t="s">
+        <v>192153.43853099982</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="187"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="188"/>
+      <c r="I3" s="188"/>
+      <c r="J3" s="189"/>
+      <c r="K3" s="96" t="s">
         <v>103</v>
       </c>
       <c r="L3" s="5"/>
-      <c r="M3" s="101">
-        <f>RESUMEN!D99</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="102"/>
+      <c r="M3" s="99">
+        <f>RESUMEN!D100</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="100"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="199"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="200"/>
-      <c r="H4" s="200"/>
-      <c r="I4" s="200"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="103" t="s">
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="190"/>
+      <c r="B4" s="191"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="191"/>
+      <c r="G4" s="191"/>
+      <c r="H4" s="191"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="L4" s="104"/>
-      <c r="M4" s="105">
-        <v>966666.66666666663</v>
-      </c>
-      <c r="N4" s="106"/>
-      <c r="O4" s="55">
+      <c r="L4" s="102"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="53">
         <f>M3/3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="186" t="s">
+    <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="202" t="s">
+      <c r="B5" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="186" t="s">
+      <c r="C5" s="177" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="191" t="s">
+      <c r="D5" s="182" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="186" t="s">
+      <c r="E5" s="177" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="186" t="s">
+      <c r="F5" s="177" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="186" t="s">
+      <c r="G5" s="177" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="188" t="s">
+      <c r="H5" s="179" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="191" t="s">
+      <c r="I5" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="184" t="s">
+      <c r="J5" s="175" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="184" t="s">
+      <c r="K5" s="175" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="184" t="s">
-        <v>129</v>
-      </c>
-      <c r="M5" s="184" t="s">
-        <v>131</v>
-      </c>
-      <c r="N5" s="184" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="187"/>
-      <c r="B6" s="203"/>
-      <c r="C6" s="187"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="187"/>
-      <c r="F6" s="187"/>
-      <c r="G6" s="187"/>
-      <c r="H6" s="189"/>
-      <c r="I6" s="192"/>
-      <c r="J6" s="190"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="185"/>
-      <c r="N6" s="185"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L5" s="175" t="s">
+        <v>120</v>
+      </c>
+      <c r="M5" s="175" t="s">
+        <v>122</v>
+      </c>
+      <c r="N5" s="175" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="178"/>
+      <c r="B6" s="194"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="180"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="181"/>
+      <c r="K6" s="176"/>
+      <c r="L6" s="181"/>
+      <c r="M6" s="176"/>
+      <c r="N6" s="176"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -3816,43 +3932,43 @@
       <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="51" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="4">
         <v>8.09</v>
       </c>
       <c r="F7" s="21">
-        <v>623232.78685699985</v>
-      </c>
-      <c r="G7" s="111">
+        <v>614901.88849999988</v>
+      </c>
+      <c r="G7" s="109">
         <f>F7</f>
-        <v>623232.78685699985</v>
-      </c>
-      <c r="H7" s="51">
+        <v>614901.88849999988</v>
+      </c>
+      <c r="H7" s="49">
         <f>F7-G7</f>
         <v>0</v>
       </c>
       <c r="I7" s="34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" s="21">
         <v>0</v>
       </c>
       <c r="K7" s="21">
-        <v>614901.88849999988</v>
+        <v>462245.18789300008</v>
       </c>
       <c r="L7" s="27"/>
       <c r="M7" s="3">
         <f>K7+J7+H7+L7</f>
-        <v>614901.88849999988</v>
+        <v>462245.18789300008</v>
       </c>
       <c r="N7" s="7">
         <f>M7*6% + M7</f>
-        <v>651796.00180999993</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>489979.89916658006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -3860,44 +3976,44 @@
       <c r="C8" s="4">
         <v>24</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="51" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="4">
         <v>2.21</v>
       </c>
       <c r="F8" s="21">
-        <v>208759.6034978492</v>
-      </c>
-      <c r="G8" s="111">
-        <v>210000</v>
-      </c>
-      <c r="H8" s="51">
+        <v>207972.93683118254</v>
+      </c>
+      <c r="G8" s="109">
+        <v>208000</v>
+      </c>
+      <c r="H8" s="49">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-1240.3965021508047</v>
+        <v>-27.063168817461701</v>
       </c>
       <c r="I8" s="34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" s="21">
         <f>M$4*E8%</f>
-        <v>21363.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K8" s="21">
         <f>M$2*E8 /100</f>
         <v>187850</v>
       </c>
-      <c r="L8" s="94"/>
+      <c r="L8" s="92"/>
       <c r="M8" s="3">
         <f>K8+J8+H8+L8</f>
-        <v>207972.93683118254</v>
+        <v>187822.93683118254</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>220451.31304105348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>199092.31304105348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
@@ -3905,45 +4021,45 @@
       <c r="C9" s="4">
         <v>25</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="4">
         <v>4.21</v>
       </c>
       <c r="F9" s="21">
-        <v>398546.93620093004</v>
-      </c>
-      <c r="G9" s="112">
+        <v>398546.60286759672</v>
+      </c>
+      <c r="G9" s="110">
         <f>449667-G34</f>
         <v>398547</v>
       </c>
-      <c r="H9" s="51">
+      <c r="H9" s="49">
         <f t="shared" si="0"/>
-        <v>-6.379906996153295E-2</v>
+        <v>-0.39713240327546373</v>
       </c>
       <c r="I9" s="34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>40696.666666666664</v>
+        <v>0</v>
       </c>
       <c r="K9" s="21">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>357850</v>
       </c>
-      <c r="L9" s="94"/>
+      <c r="L9" s="92"/>
       <c r="M9" s="3">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>398546.60286759672</v>
+        <v>357849.60286759672</v>
       </c>
       <c r="N9" s="7">
         <f t="shared" si="1"/>
-        <v>422459.39903965255</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>379320.57903965254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
@@ -3951,7 +4067,7 @@
       <c r="C10" s="4">
         <v>26</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" s="51" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="4">
@@ -3960,11 +4076,11 @@
       <c r="F10" s="21">
         <v>268853.33333333331</v>
       </c>
-      <c r="G10" s="111">
+      <c r="G10" s="109">
         <f>F10</f>
         <v>268853.33333333331</v>
       </c>
-      <c r="H10" s="51">
+      <c r="H10" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3973,23 +4089,23 @@
       </c>
       <c r="J10" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K10" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L10" s="94"/>
+      <c r="L10" s="92"/>
       <c r="M10" s="3">
         <f t="shared" si="4"/>
-        <v>268853.33333333331</v>
+        <v>241400</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" si="1"/>
-        <v>284984.53333333333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>255884</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -3997,7 +4113,7 @@
       <c r="C11" s="4">
         <v>27</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="51" t="s">
         <v>33</v>
       </c>
       <c r="E11" s="4">
@@ -4006,37 +4122,37 @@
       <c r="F11" s="21">
         <v>324706.66666666669</v>
       </c>
-      <c r="G11" s="111">
+      <c r="G11" s="109">
         <f>F11</f>
         <v>324706.66666666669</v>
       </c>
-      <c r="H11" s="51">
+      <c r="H11" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K11" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L11" s="94"/>
+      <c r="L11" s="92"/>
       <c r="M11" s="3">
         <f t="shared" si="4"/>
-        <v>324706.66666666669</v>
+        <v>291550</v>
       </c>
       <c r="N11" s="7">
         <f t="shared" si="1"/>
-        <v>344189.06666666671</v>
+        <v>309043</v>
       </c>
       <c r="P11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>34</v>
       </c>
@@ -4044,7 +4160,7 @@
       <c r="C12" s="4">
         <v>28</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E12" s="4">
@@ -4053,11 +4169,11 @@
       <c r="F12" s="21">
         <v>268853.33333333331</v>
       </c>
-      <c r="G12" s="112">
+      <c r="G12" s="110">
         <f>F12</f>
         <v>268853.33333333331</v>
       </c>
-      <c r="H12" s="51">
+      <c r="H12" s="49">
         <f>F12-G12</f>
         <v>0</v>
       </c>
@@ -4066,23 +4182,23 @@
       </c>
       <c r="J12" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K12" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L12" s="94"/>
+      <c r="L12" s="92"/>
       <c r="M12" s="3">
         <f t="shared" si="4"/>
-        <v>268853.33333333331</v>
+        <v>241400</v>
       </c>
       <c r="N12" s="7">
         <f t="shared" si="1"/>
-        <v>284984.53333333333</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>255884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
@@ -4090,7 +4206,7 @@
       <c r="C13" s="4">
         <v>29</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" s="51" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="4">
@@ -4099,11 +4215,11 @@
       <c r="F13" s="21">
         <v>324707.48408590845</v>
       </c>
-      <c r="G13" s="112">
+      <c r="G13" s="110">
         <f>380560-G50</f>
         <v>324706.66666666669</v>
       </c>
-      <c r="H13" s="51">
+      <c r="H13" s="49">
         <f t="shared" si="0"/>
         <v>0.81741924176458269</v>
       </c>
@@ -4112,23 +4228,23 @@
       </c>
       <c r="J13" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K13" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L13" s="94"/>
+      <c r="L13" s="92"/>
       <c r="M13" s="3">
         <f t="shared" si="4"/>
-        <v>324707.48408590845</v>
+        <v>291550.81741924176</v>
       </c>
       <c r="N13" s="7">
         <f t="shared" si="1"/>
-        <v>344189.93313106295</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>309043.86646439624</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>36</v>
       </c>
@@ -4136,42 +4252,45 @@
       <c r="C14" s="4">
         <v>30</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" s="51" t="s">
         <v>37</v>
       </c>
       <c r="E14" s="4">
         <v>2.84</v>
       </c>
       <c r="F14" s="21">
-        <v>268853.33333333331</v>
-      </c>
-      <c r="G14" s="111"/>
-      <c r="H14" s="51">
+        <v>537706.66666666663</v>
+      </c>
+      <c r="G14" s="109">
+        <f>284985</f>
+        <v>284985</v>
+      </c>
+      <c r="H14" s="49">
         <f t="shared" si="0"/>
-        <v>268853.33333333331</v>
+        <v>252721.66666666663</v>
       </c>
       <c r="I14" s="34">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K14" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L14" s="94"/>
+      <c r="L14" s="92"/>
       <c r="M14" s="3">
         <f t="shared" si="4"/>
-        <v>537706.66666666663</v>
+        <v>494121.66666666663</v>
       </c>
       <c r="N14" s="7">
         <f t="shared" si="1"/>
-        <v>569969.06666666665</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>523768.96666666662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
@@ -4179,40 +4298,45 @@
       <c r="C15" s="4">
         <v>31</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="51" t="s">
         <v>109</v>
       </c>
       <c r="E15" s="4">
         <v>3.43</v>
       </c>
       <c r="F15" s="21">
-        <v>649413.20432986738</v>
-      </c>
-      <c r="G15" s="112"/>
-      <c r="H15" s="51">
+        <v>1032567.0632563261</v>
+      </c>
+      <c r="G15" s="110">
+        <f>1116120-G35</f>
+        <v>965600</v>
+      </c>
+      <c r="H15" s="49">
         <f t="shared" si="0"/>
-        <v>649413.20432986738</v>
-      </c>
-      <c r="I15" s="34"/>
+        <v>66967.063256326132</v>
+      </c>
+      <c r="I15" s="34">
+        <v>19</v>
+      </c>
       <c r="J15" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K15" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L15" s="94"/>
+      <c r="L15" s="92"/>
       <c r="M15" s="3">
         <f t="shared" si="4"/>
-        <v>974119.87099653413</v>
+        <v>358517.06325632613</v>
       </c>
       <c r="N15" s="7">
         <f t="shared" si="1"/>
-        <v>1032567.0632563261</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>380028.08705170569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>38</v>
       </c>
@@ -4220,45 +4344,45 @@
       <c r="C16" s="4">
         <v>32</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="51" t="s">
         <v>107</v>
       </c>
       <c r="E16" s="4">
         <v>2.84</v>
       </c>
       <c r="F16" s="21">
-        <v>287767.41316033335</v>
-      </c>
-      <c r="G16" s="112">
-        <f>334154-G49</f>
-        <v>287767.33333333331</v>
-      </c>
-      <c r="H16" s="51">
+        <v>268853.41316033335</v>
+      </c>
+      <c r="G16" s="110">
+        <f>315240-G49</f>
+        <v>268853.33333333331</v>
+      </c>
+      <c r="H16" s="49">
         <f t="shared" si="0"/>
         <v>7.9827000037766993E-2</v>
       </c>
       <c r="I16" s="34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L16" s="94"/>
+      <c r="L16" s="92"/>
       <c r="M16" s="3">
         <f t="shared" si="4"/>
-        <v>268853.41316033335</v>
+        <v>241400.07982700004</v>
       </c>
       <c r="N16" s="7">
         <f t="shared" si="1"/>
-        <v>284984.61794995336</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>255884.08461662004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
@@ -4266,47 +4390,45 @@
       <c r="C17" s="4">
         <v>33</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="51" t="s">
         <v>39</v>
       </c>
       <c r="E17" s="4">
         <v>3.43</v>
       </c>
       <c r="F17" s="21">
-        <v>344706.64067778148</v>
-      </c>
-      <c r="G17" s="111">
-        <f>438427-G47-G48</f>
-        <v>344707</v>
-      </c>
-      <c r="H17" s="51">
+        <v>344706.30734444817</v>
+      </c>
+      <c r="G17" s="109">
+        <f>438426-G47-G48</f>
+        <v>344706</v>
+      </c>
+      <c r="H17" s="49">
         <f t="shared" si="0"/>
-        <v>-0.35932221851544455</v>
+        <v>0.30734444817062467</v>
       </c>
       <c r="I17" s="34">
         <v>13</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L17" s="94">
-        <v>20000</v>
-      </c>
+      <c r="L17" s="92"/>
       <c r="M17" s="3">
         <f t="shared" si="4"/>
-        <v>344706.30734444817</v>
+        <v>291550.30734444817</v>
       </c>
       <c r="N17" s="7">
         <f t="shared" si="1"/>
-        <v>365388.68578511506</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>309043.32578511507</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
@@ -4314,48 +4436,48 @@
       <c r="C18" s="4">
         <v>34</v>
       </c>
-      <c r="D18" s="53" t="s">
-        <v>119</v>
+      <c r="D18" s="51" t="s">
+        <v>117</v>
       </c>
       <c r="E18" s="4">
         <v>2.84</v>
       </c>
       <c r="F18" s="21">
-        <v>268853.76046658464</v>
-      </c>
-      <c r="G18" s="111">
-        <f>342182.59-G51</f>
-        <v>288222.59000000003</v>
-      </c>
-      <c r="H18" s="51">
+        <v>249484.50379991793</v>
+      </c>
+      <c r="G18" s="109">
+        <f>303445-G51</f>
+        <v>249485</v>
+      </c>
+      <c r="H18" s="49">
         <f t="shared" si="0"/>
-        <v>-19368.829533415381</v>
+        <v>-0.49620008206693456</v>
       </c>
       <c r="I18" s="34">
         <v>11</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K18" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L18" s="94"/>
+      <c r="L18" s="92"/>
       <c r="M18" s="3">
         <f t="shared" si="4"/>
-        <v>249484.50379991793</v>
+        <v>241399.50379991793</v>
       </c>
       <c r="N18" s="7">
         <f t="shared" si="1"/>
-        <v>264453.57402791298</v>
+        <v>255883.47402791301</v>
       </c>
       <c r="P18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>40</v>
       </c>
@@ -4363,45 +4485,47 @@
       <c r="C19" s="4">
         <v>35</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="51" t="s">
         <v>42</v>
       </c>
       <c r="E19" s="4">
         <v>3.43</v>
       </c>
       <c r="F19" s="21">
-        <v>324707.15298183478</v>
-      </c>
-      <c r="G19" s="112">
+        <v>324706.81964850146</v>
+      </c>
+      <c r="G19" s="110">
         <f>375827-G41</f>
         <v>324707</v>
       </c>
-      <c r="H19" s="51">
+      <c r="H19" s="49">
         <f t="shared" si="0"/>
-        <v>0.1529818347771652</v>
+        <v>-0.18035149853676558</v>
       </c>
       <c r="I19" s="34">
         <v>9</v>
       </c>
       <c r="J19" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K19" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L19" s="94"/>
+      <c r="L19" s="92">
+        <v>20000</v>
+      </c>
       <c r="M19" s="3">
         <f t="shared" si="4"/>
-        <v>324706.81964850146</v>
+        <v>311549.81964850146</v>
       </c>
       <c r="N19" s="7">
         <f t="shared" si="1"/>
-        <v>344189.22882741154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>330242.80882741156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -4409,7 +4533,7 @@
       <c r="C20" s="4">
         <v>36</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="51" t="s">
         <v>44</v>
       </c>
       <c r="E20" s="4">
@@ -4418,11 +4542,11 @@
       <c r="F20" s="21">
         <v>268852.98919040803</v>
       </c>
-      <c r="G20" s="111">
+      <c r="G20" s="109">
         <f>315240-G38</f>
         <v>268853.33333333331</v>
       </c>
-      <c r="H20" s="51">
+      <c r="H20" s="49">
         <f t="shared" si="0"/>
         <v>-0.34414292528526857</v>
       </c>
@@ -4431,23 +4555,23 @@
       </c>
       <c r="J20" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K20" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L20" s="94"/>
+      <c r="L20" s="92"/>
       <c r="M20" s="3">
         <f t="shared" si="4"/>
-        <v>268852.98919040803</v>
+        <v>241399.65585707471</v>
       </c>
       <c r="N20" s="7">
         <f t="shared" si="1"/>
-        <v>284984.16854183254</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+        <v>255883.63520849921</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -4455,45 +4579,45 @@
       <c r="C21" s="4">
         <v>37</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="51" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="4">
         <v>3.43</v>
       </c>
       <c r="F21" s="21">
-        <v>324706.55530846264</v>
-      </c>
-      <c r="G21" s="111">
-        <f>375827-G45</f>
-        <v>324707</v>
-      </c>
-      <c r="H21" s="51">
+        <v>344188.59529363707</v>
+      </c>
+      <c r="G21" s="109">
+        <f>398375.8-G45</f>
+        <v>344188.6</v>
+      </c>
+      <c r="H21" s="49">
         <f t="shared" si="0"/>
-        <v>-0.44469153735553846</v>
+        <v>-4.7063629026524723E-3</v>
       </c>
       <c r="I21" s="34">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J21" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K21" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L21" s="94"/>
+      <c r="L21" s="92"/>
       <c r="M21" s="3">
         <f t="shared" si="4"/>
-        <v>324706.22197512933</v>
+        <v>291549.9952936371</v>
       </c>
       <c r="N21" s="7">
         <f t="shared" si="1"/>
-        <v>344188.59529363707</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>309042.99501125532</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>46</v>
       </c>
@@ -4501,7 +4625,7 @@
       <c r="C22" s="4">
         <v>38</v>
       </c>
-      <c r="D22" s="74" t="s">
+      <c r="D22" s="72" t="s">
         <v>100</v>
       </c>
       <c r="E22" s="4">
@@ -4510,36 +4634,36 @@
       <c r="F22" s="21">
         <v>268853.33333333331</v>
       </c>
-      <c r="G22" s="111">
+      <c r="G22" s="109">
         <f>F22</f>
         <v>268853.33333333331</v>
       </c>
-      <c r="H22" s="51">
+      <c r="H22" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J22" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K22" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L22" s="94"/>
+      <c r="L22" s="92"/>
       <c r="M22" s="3">
         <f t="shared" si="4"/>
-        <v>268853.33333333331</v>
+        <v>241400</v>
       </c>
       <c r="N22" s="7">
         <f t="shared" si="1"/>
-        <v>284984.53333333333</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+        <v>255884</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
@@ -4547,45 +4671,47 @@
       <c r="C23" s="4">
         <v>39</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="51" t="s">
         <v>47</v>
       </c>
       <c r="E23" s="4">
         <v>3.43</v>
       </c>
       <c r="F23" s="21">
-        <v>665935.33457008889</v>
-      </c>
-      <c r="G23" s="112">
-        <f>400000-G46</f>
-        <v>349826.66666666669</v>
-      </c>
-      <c r="H23" s="51">
+        <v>640815.33457008889</v>
+      </c>
+      <c r="G23" s="110">
+        <f>690000-G46</f>
+        <v>642666.66666666663</v>
+      </c>
+      <c r="H23" s="49">
         <f t="shared" si="0"/>
-        <v>316108.6679034222</v>
+        <v>-1851.3320965777384</v>
       </c>
       <c r="I23" s="34">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J23" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K23" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L23" s="94"/>
+      <c r="L23" s="92">
+        <v>20000</v>
+      </c>
       <c r="M23" s="3">
         <f t="shared" si="4"/>
-        <v>640815.33457008889</v>
+        <v>309698.66790342226</v>
       </c>
       <c r="N23" s="7">
         <f t="shared" si="1"/>
-        <v>679264.25464429427</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>328280.58797762758</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>48</v>
       </c>
@@ -4593,45 +4719,45 @@
       <c r="C24" s="4">
         <v>40</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="51" t="s">
         <v>49</v>
       </c>
       <c r="E24" s="4">
         <v>2.84</v>
       </c>
       <c r="F24" s="21">
-        <v>268258.70675440802</v>
-      </c>
-      <c r="G24" s="111">
-        <f>315500-G37</f>
-        <v>269113.33333333331</v>
-      </c>
-      <c r="H24" s="51">
+        <v>267998.70675440802</v>
+      </c>
+      <c r="G24" s="109">
+        <f>320000-G37</f>
+        <v>273613.33333333331</v>
+      </c>
+      <c r="H24" s="49">
         <f t="shared" si="0"/>
-        <v>-854.62657892529387</v>
-      </c>
-      <c r="I24" s="82">
-        <v>16</v>
+        <v>-5614.6265789252939</v>
+      </c>
+      <c r="I24" s="80">
+        <v>12</v>
       </c>
       <c r="J24" s="21">
         <f t="shared" si="2"/>
-        <v>27453.333333333332</v>
+        <v>0</v>
       </c>
       <c r="K24" s="21">
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L24" s="94"/>
+      <c r="L24" s="92"/>
       <c r="M24" s="3">
         <f t="shared" si="4"/>
-        <v>267998.70675440802</v>
+        <v>235785.37342107471</v>
       </c>
       <c r="N24" s="7">
         <f t="shared" si="1"/>
-        <v>284078.62915967248</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>249932.49582633917</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -4639,51 +4765,47 @@
       <c r="C25" s="4">
         <v>41</v>
       </c>
-      <c r="D25" s="53" t="s">
-        <v>132</v>
+      <c r="D25" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="E25" s="4">
         <v>3.43</v>
       </c>
       <c r="F25" s="21">
-        <v>365389.07</v>
-      </c>
-      <c r="G25" s="112">
-        <f>F25</f>
-        <v>365389.07</v>
-      </c>
-      <c r="H25" s="51">
+        <v>470481.66666666669</v>
+      </c>
+      <c r="G25" s="110">
+        <v>498710</v>
+      </c>
+      <c r="H25" s="49">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-28228.333333333314</v>
       </c>
       <c r="I25" s="34">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J25" s="21">
         <f t="shared" si="2"/>
-        <v>33156.666666666672</v>
+        <v>0</v>
       </c>
       <c r="K25" s="21">
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L25" s="95">
-        <f>K25*0.5</f>
-        <v>145775</v>
-      </c>
+      <c r="L25" s="93"/>
       <c r="M25" s="3">
         <f t="shared" si="4"/>
-        <v>470481.66666666669</v>
+        <v>263321.66666666669</v>
       </c>
       <c r="N25" s="7">
         <f t="shared" si="1"/>
-        <v>498710.56666666671</v>
-      </c>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+        <v>279120.96666666667</v>
+      </c>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="56"/>
+      <c r="R25" s="56"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -4691,43 +4813,45 @@
       <c r="C26" s="4">
         <v>42</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="51" t="s">
         <v>51</v>
       </c>
       <c r="E26" s="4">
         <v>6</v>
       </c>
       <c r="F26" s="21">
-        <v>-1020518.0073339629</v>
-      </c>
-      <c r="G26" s="112">
-        <f>-G30-G31</f>
-        <v>-103186.66666666666</v>
-      </c>
-      <c r="H26" s="52">
+        <v>-349331.34066729632</v>
+      </c>
+      <c r="G26" s="110">
+        <f>900000+500000-G30-G31-G36</f>
+        <v>1249480</v>
+      </c>
+      <c r="H26" s="50">
         <f t="shared" si="0"/>
-        <v>-917331.34066729632</v>
-      </c>
-      <c r="I26" s="34"/>
+        <v>-1598811.3406672962</v>
+      </c>
+      <c r="I26" s="205">
+        <v>46081</v>
+      </c>
       <c r="J26" s="21">
         <f t="shared" si="2"/>
-        <v>57999.999999999993</v>
+        <v>0</v>
       </c>
       <c r="K26" s="21">
         <f t="shared" si="3"/>
         <v>510000</v>
       </c>
-      <c r="L26" s="94"/>
+      <c r="L26" s="92"/>
       <c r="M26" s="3">
         <f t="shared" si="4"/>
-        <v>-349331.34066729632</v>
+        <v>-1088811.3406672962</v>
       </c>
       <c r="N26" s="7">
         <f t="shared" si="1"/>
-        <v>-370291.22110733407</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-1154140.0211073339</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -4735,46 +4859,46 @@
       <c r="C27" s="4">
         <v>43</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="51" t="s">
         <v>53</v>
       </c>
       <c r="E27" s="4">
         <v>5.89</v>
       </c>
       <c r="F27" s="21">
-        <v>550998.03795193194</v>
-      </c>
-      <c r="G27" s="111">
-        <f>660811-G39-G40</f>
-        <v>550997.66666666663</v>
-      </c>
-      <c r="H27" s="51">
+        <v>557587.03795193194</v>
+      </c>
+      <c r="G27" s="109">
+        <f>667400-G39-G40</f>
+        <v>557586.66666666663</v>
+      </c>
+      <c r="H27" s="49">
         <f t="shared" si="0"/>
         <v>0.37128526531159878</v>
       </c>
       <c r="I27" s="34">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J27" s="21">
         <f t="shared" si="2"/>
-        <v>56936.666666666657</v>
+        <v>0</v>
       </c>
       <c r="K27" s="21">
         <f t="shared" si="3"/>
         <v>500650</v>
       </c>
-      <c r="L27" s="94"/>
+      <c r="L27" s="92"/>
       <c r="M27" s="3">
         <f t="shared" si="4"/>
-        <v>557587.03795193194</v>
+        <v>500650.37128526531</v>
       </c>
       <c r="N27" s="7">
         <f t="shared" si="1"/>
-        <v>591042.26022904785</v>
-      </c>
-      <c r="R27" s="58"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+        <v>530689.39356238127</v>
+      </c>
+      <c r="R27" s="56"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -4782,45 +4906,45 @@
       <c r="C28" s="4">
         <v>44</v>
       </c>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="51" t="s">
         <v>55</v>
       </c>
       <c r="E28" s="4">
         <v>5.89</v>
       </c>
       <c r="F28" s="21">
-        <v>556661.17449320748</v>
-      </c>
-      <c r="G28" s="111">
-        <f>658000-G32-G33</f>
-        <v>557653.33333333337</v>
-      </c>
-      <c r="H28" s="51">
+        <v>556594.50782654074</v>
+      </c>
+      <c r="G28" s="109">
+        <f>657000-G32-G33</f>
+        <v>556653.33333333337</v>
+      </c>
+      <c r="H28" s="49">
         <f t="shared" si="0"/>
-        <v>-992.15884012589231</v>
+        <v>-58.825506792636588</v>
       </c>
       <c r="I28" s="34">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J28" s="21">
         <f t="shared" si="2"/>
-        <v>56936.666666666657</v>
+        <v>0</v>
       </c>
       <c r="K28" s="21">
         <f t="shared" si="3"/>
         <v>500650</v>
       </c>
-      <c r="L28" s="94"/>
+      <c r="L28" s="92"/>
       <c r="M28" s="3">
         <f t="shared" si="4"/>
-        <v>556594.50782654074</v>
+        <v>500591.17449320736</v>
       </c>
       <c r="N28" s="7">
         <f t="shared" si="1"/>
-        <v>589990.17829613318</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>530626.64496279985</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -4828,48 +4952,53 @@
       <c r="C29" s="4">
         <v>45</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" s="51" t="s">
         <v>57</v>
       </c>
       <c r="E29" s="4">
         <v>5.89</v>
       </c>
       <c r="F29" s="21">
-        <v>1115174.0372900332</v>
-      </c>
-      <c r="G29" s="112"/>
-      <c r="H29" s="52">
+        <v>1773126.346194102</v>
+      </c>
+      <c r="G29" s="110">
+        <f>2130010-G42-G43-G44</f>
+        <v>1645335.6</v>
+      </c>
+      <c r="H29" s="50">
         <f t="shared" si="0"/>
-        <v>1115174.0372900332</v>
-      </c>
-      <c r="I29" s="34"/>
+        <v>127790.74619410187</v>
+      </c>
+      <c r="I29" s="34">
+        <v>17</v>
+      </c>
       <c r="J29" s="21">
         <f t="shared" si="2"/>
-        <v>56936.666666666657</v>
+        <v>0</v>
       </c>
       <c r="K29" s="21">
         <f t="shared" si="3"/>
         <v>500650</v>
       </c>
-      <c r="L29" s="94"/>
+      <c r="L29" s="92"/>
       <c r="M29" s="3">
         <f t="shared" si="4"/>
-        <v>1672760.7039566999</v>
+        <v>628440.74619410187</v>
       </c>
       <c r="N29" s="7">
         <f t="shared" si="1"/>
-        <v>1773126.346194102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="48" t="s">
+        <v>666147.19096574793</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
         <v>1</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="51" t="s">
         <v>51</v>
       </c>
       <c r="E30" s="4">
@@ -4878,42 +5007,42 @@
       <c r="F30" s="21">
         <v>51120</v>
       </c>
-      <c r="G30" s="111">
+      <c r="G30" s="109">
         <f>F30</f>
         <v>51120</v>
       </c>
-      <c r="H30" s="51">
+      <c r="H30" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I30" s="34"/>
       <c r="J30" s="21">
         <f t="shared" si="2"/>
-        <v>5220</v>
+        <v>0</v>
       </c>
       <c r="K30" s="21">
         <f t="shared" si="3"/>
         <v>45900</v>
       </c>
-      <c r="L30" s="94"/>
+      <c r="L30" s="92"/>
       <c r="M30" s="3">
         <f t="shared" si="4"/>
-        <v>51120</v>
+        <v>45900</v>
       </c>
       <c r="N30" s="7">
         <f t="shared" si="1"/>
-        <v>54187.199999999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="48" t="s">
+        <v>48654</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
         <v>2</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="51" t="s">
         <v>51</v>
       </c>
       <c r="E31" s="4">
@@ -4922,42 +5051,42 @@
       <c r="F31" s="21">
         <v>52066.666666666664</v>
       </c>
-      <c r="G31" s="111">
+      <c r="G31" s="109">
         <f>F31</f>
         <v>52066.666666666664</v>
       </c>
-      <c r="H31" s="51">
+      <c r="H31" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I31" s="34"/>
       <c r="J31" s="21">
         <f t="shared" si="2"/>
-        <v>5316.666666666667</v>
+        <v>0</v>
       </c>
       <c r="K31" s="21">
         <f t="shared" si="3"/>
         <v>46750</v>
       </c>
-      <c r="L31" s="94"/>
+      <c r="L31" s="92"/>
       <c r="M31" s="3">
         <f t="shared" si="4"/>
-        <v>52066.666666666664</v>
+        <v>46750</v>
       </c>
       <c r="N31" s="7">
         <f t="shared" si="1"/>
-        <v>55190.666666666664</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="48" t="s">
+        <v>49555</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
         <v>3</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="51" t="s">
         <v>55</v>
       </c>
       <c r="E32" s="4">
@@ -4966,42 +5095,42 @@
       <c r="F32" s="21">
         <v>42600</v>
       </c>
-      <c r="G32" s="111">
+      <c r="G32" s="109">
         <f>F32</f>
         <v>42600</v>
       </c>
-      <c r="H32" s="51">
+      <c r="H32" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I32" s="34"/>
       <c r="J32" s="21">
         <f t="shared" si="2"/>
-        <v>4350</v>
+        <v>0</v>
       </c>
       <c r="K32" s="21">
         <f t="shared" si="3"/>
         <v>38250</v>
       </c>
-      <c r="L32" s="73"/>
+      <c r="L32" s="71"/>
       <c r="M32" s="3">
         <f t="shared" si="4"/>
-        <v>42600</v>
+        <v>38250</v>
       </c>
       <c r="N32" s="7">
         <f t="shared" si="1"/>
-        <v>45156</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="48" t="s">
+        <v>40545</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4">
         <v>4</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="D33" s="51" t="s">
         <v>55</v>
       </c>
       <c r="E33" s="4">
@@ -5010,42 +5139,42 @@
       <c r="F33" s="21">
         <v>57746.666666666664</v>
       </c>
-      <c r="G33" s="111">
+      <c r="G33" s="109">
         <f t="shared" ref="G33:G34" si="5">F33</f>
         <v>57746.666666666664</v>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I33" s="34"/>
       <c r="J33" s="21">
         <f t="shared" si="2"/>
-        <v>5896.6666666666661</v>
+        <v>0</v>
       </c>
       <c r="K33" s="21">
         <f t="shared" si="3"/>
         <v>51850</v>
       </c>
-      <c r="L33" s="73"/>
+      <c r="L33" s="71"/>
       <c r="M33" s="3">
         <f t="shared" si="4"/>
-        <v>57746.666666666664</v>
+        <v>51850</v>
       </c>
       <c r="N33" s="7">
         <f t="shared" si="1"/>
-        <v>61211.466666666667</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="48" t="s">
+        <v>54961</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4">
         <v>5</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E34" s="4">
@@ -5054,83 +5183,86 @@
       <c r="F34" s="21">
         <v>51120</v>
       </c>
-      <c r="G34" s="111">
-        <f t="shared" si="5"/>
+      <c r="G34" s="109">
+        <f>F34</f>
         <v>51120</v>
       </c>
-      <c r="H34" s="51">
+      <c r="H34" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I34" s="34"/>
       <c r="J34" s="21">
         <f t="shared" si="2"/>
-        <v>5220</v>
+        <v>0</v>
       </c>
       <c r="K34" s="21">
         <f t="shared" si="3"/>
         <v>45900</v>
       </c>
-      <c r="L34" s="73"/>
+      <c r="L34" s="71"/>
       <c r="M34" s="3">
         <f t="shared" si="4"/>
-        <v>51120</v>
+        <v>45900</v>
       </c>
       <c r="N34" s="7">
         <f t="shared" si="1"/>
-        <v>54187.199999999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="48" t="s">
+        <v>48654</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
         <v>6</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="D35" s="51" t="s">
         <v>109</v>
       </c>
       <c r="E35" s="4">
         <v>0.5</v>
       </c>
       <c r="F35" s="3">
-        <v>94666.666666666672</v>
-      </c>
-      <c r="G35" s="112"/>
-      <c r="H35" s="51">
+        <v>150520</v>
+      </c>
+      <c r="G35" s="110">
+        <f>F35</f>
+        <v>150520</v>
+      </c>
+      <c r="H35" s="49">
         <f t="shared" si="0"/>
-        <v>94666.666666666672</v>
+        <v>0</v>
       </c>
       <c r="I35" s="34"/>
       <c r="J35" s="21">
         <f t="shared" si="2"/>
-        <v>4833.333333333333</v>
+        <v>0</v>
       </c>
       <c r="K35" s="21">
         <f t="shared" si="3"/>
         <v>42500</v>
       </c>
-      <c r="L35" s="73"/>
+      <c r="L35" s="71"/>
       <c r="M35" s="3">
         <f t="shared" si="4"/>
-        <v>142000</v>
+        <v>42500</v>
       </c>
       <c r="N35" s="7">
         <f t="shared" si="1"/>
-        <v>150520</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="48" t="s">
+        <v>45050</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4">
         <v>7</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="51" t="s">
         <v>51</v>
       </c>
       <c r="E36" s="4">
@@ -5139,42 +5271,42 @@
       <c r="F36" s="21">
         <v>47333.333333333336</v>
       </c>
-      <c r="G36" s="111">
+      <c r="G36" s="109">
         <f>F36</f>
         <v>47333.333333333336</v>
       </c>
-      <c r="H36" s="51">
+      <c r="H36" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I36" s="34"/>
       <c r="J36" s="21">
         <f t="shared" si="2"/>
-        <v>4833.333333333333</v>
+        <v>0</v>
       </c>
       <c r="K36" s="21">
         <f t="shared" si="3"/>
         <v>42500</v>
       </c>
-      <c r="L36" s="73"/>
+      <c r="L36" s="71"/>
       <c r="M36" s="3">
         <f t="shared" si="4"/>
-        <v>47333.333333333336</v>
+        <v>42500</v>
       </c>
       <c r="N36" s="7">
         <f t="shared" si="1"/>
-        <v>50173.333333333336</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
+        <v>45050</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
         <v>8</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="D37" s="51" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="4">
@@ -5183,42 +5315,42 @@
       <c r="F37" s="21">
         <v>46386.666666666664</v>
       </c>
-      <c r="G37" s="111">
+      <c r="G37" s="109">
         <f t="shared" ref="G37:G41" si="6">F37</f>
         <v>46386.666666666664</v>
       </c>
-      <c r="H37" s="51">
+      <c r="H37" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I37" s="34"/>
       <c r="J37" s="21">
         <f t="shared" si="2"/>
-        <v>4736.6666666666661</v>
+        <v>0</v>
       </c>
       <c r="K37" s="21">
         <f t="shared" si="3"/>
         <v>41650</v>
       </c>
-      <c r="L37" s="73"/>
+      <c r="L37" s="71"/>
       <c r="M37" s="3">
         <f t="shared" si="4"/>
-        <v>46386.666666666664</v>
+        <v>41650</v>
       </c>
       <c r="N37" s="7">
         <f t="shared" si="1"/>
-        <v>49169.866666666661</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="48" t="s">
+        <v>44149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
         <v>9</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" s="51" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="4">
@@ -5227,42 +5359,42 @@
       <c r="F38" s="21">
         <v>46386.666666666664</v>
       </c>
-      <c r="G38" s="111">
+      <c r="G38" s="109">
         <f t="shared" si="6"/>
         <v>46386.666666666664</v>
       </c>
-      <c r="H38" s="51">
+      <c r="H38" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I38" s="34"/>
       <c r="J38" s="21">
         <f t="shared" si="2"/>
-        <v>4736.6666666666661</v>
+        <v>0</v>
       </c>
       <c r="K38" s="21">
         <f t="shared" si="3"/>
         <v>41650</v>
       </c>
-      <c r="L38" s="73"/>
+      <c r="L38" s="71"/>
       <c r="M38" s="3">
         <f t="shared" si="4"/>
-        <v>46386.666666666664</v>
+        <v>41650</v>
       </c>
       <c r="N38" s="7">
         <f t="shared" si="1"/>
-        <v>49169.866666666661</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="48" t="s">
+        <v>44149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
         <v>10</v>
       </c>
-      <c r="D39" s="53" t="s">
+      <c r="D39" s="51" t="s">
         <v>53</v>
       </c>
       <c r="E39" s="4">
@@ -5271,42 +5403,42 @@
       <c r="F39" s="21">
         <v>55853.333333333336</v>
       </c>
-      <c r="G39" s="111">
+      <c r="G39" s="109">
         <f t="shared" si="6"/>
         <v>55853.333333333336</v>
       </c>
-      <c r="H39" s="51">
+      <c r="H39" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I39" s="34"/>
       <c r="J39" s="21">
         <f t="shared" si="2"/>
-        <v>5703.333333333333</v>
+        <v>0</v>
       </c>
       <c r="K39" s="21">
         <f t="shared" si="3"/>
         <v>50150</v>
       </c>
-      <c r="L39" s="73"/>
+      <c r="L39" s="71"/>
       <c r="M39" s="3">
         <f t="shared" si="4"/>
-        <v>55853.333333333336</v>
+        <v>50150</v>
       </c>
       <c r="N39" s="7">
         <f t="shared" si="1"/>
-        <v>59204.533333333333</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="48" t="s">
+        <v>53159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
         <v>11</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" s="51" t="s">
         <v>53</v>
       </c>
       <c r="E40" s="4">
@@ -5315,42 +5447,42 @@
       <c r="F40" s="21">
         <v>53960</v>
       </c>
-      <c r="G40" s="111">
+      <c r="G40" s="109">
         <f t="shared" si="6"/>
         <v>53960</v>
       </c>
-      <c r="H40" s="51">
+      <c r="H40" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="21">
         <f t="shared" si="2"/>
-        <v>5509.9999999999991</v>
+        <v>0</v>
       </c>
       <c r="K40" s="21">
         <f t="shared" si="3"/>
         <v>48450</v>
       </c>
-      <c r="L40" s="73"/>
+      <c r="L40" s="71"/>
       <c r="M40" s="3">
         <f t="shared" si="4"/>
-        <v>53960</v>
+        <v>48450</v>
       </c>
       <c r="N40" s="7">
         <f t="shared" si="1"/>
-        <v>57197.599999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="48" t="s">
+        <v>51357</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
         <v>12</v>
       </c>
-      <c r="D41" s="53" t="s">
+      <c r="D41" s="51" t="s">
         <v>42</v>
       </c>
       <c r="E41" s="4">
@@ -5359,260 +5491,269 @@
       <c r="F41" s="21">
         <v>51120</v>
       </c>
-      <c r="G41" s="111">
+      <c r="G41" s="109">
         <f t="shared" si="6"/>
         <v>51120</v>
       </c>
-      <c r="H41" s="51">
+      <c r="H41" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I41" s="34"/>
       <c r="J41" s="21">
         <f t="shared" si="2"/>
-        <v>5220</v>
+        <v>0</v>
       </c>
       <c r="K41" s="21">
         <f t="shared" si="3"/>
         <v>45900</v>
       </c>
-      <c r="L41" s="73"/>
+      <c r="L41" s="71"/>
       <c r="M41" s="3">
         <f t="shared" si="4"/>
-        <v>51120</v>
+        <v>45900</v>
       </c>
       <c r="N41" s="7">
         <f t="shared" si="1"/>
-        <v>54187.199999999997</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="48" t="s">
+        <v>48654</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
         <v>13</v>
       </c>
-      <c r="D42" s="53" t="s">
+      <c r="D42" s="51" t="s">
         <v>57</v>
       </c>
       <c r="E42" s="4">
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="21">
-        <v>104133.33333333333</v>
-      </c>
-      <c r="G42" s="111"/>
-      <c r="H42" s="51">
+        <v>165572</v>
+      </c>
+      <c r="G42" s="109">
+        <f>F42</f>
+        <v>165572</v>
+      </c>
+      <c r="H42" s="49">
         <f t="shared" si="0"/>
-        <v>104133.33333333333</v>
+        <v>0</v>
       </c>
       <c r="I42" s="34"/>
       <c r="J42" s="21">
         <f t="shared" si="2"/>
-        <v>5316.666666666667</v>
+        <v>0</v>
       </c>
       <c r="K42" s="21">
         <f t="shared" si="3"/>
         <v>46750</v>
       </c>
-      <c r="L42" s="73"/>
+      <c r="L42" s="71"/>
       <c r="M42" s="3">
         <f t="shared" si="4"/>
-        <v>156200</v>
+        <v>46750</v>
       </c>
       <c r="N42" s="7">
         <f t="shared" si="1"/>
-        <v>165572</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="48" t="s">
+        <v>49555</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
         <v>14</v>
       </c>
-      <c r="D43" s="53" t="s">
+      <c r="D43" s="51" t="s">
         <v>57</v>
       </c>
       <c r="E43" s="4">
         <v>0.45</v>
       </c>
       <c r="F43" s="21">
-        <v>85200</v>
-      </c>
-      <c r="G43" s="111"/>
-      <c r="H43" s="51">
+        <v>135468</v>
+      </c>
+      <c r="G43" s="109">
+        <f t="shared" ref="G43:G44" si="7">F43</f>
+        <v>135468</v>
+      </c>
+      <c r="H43" s="49">
         <f t="shared" si="0"/>
-        <v>85200</v>
+        <v>0</v>
       </c>
       <c r="I43" s="34"/>
       <c r="J43" s="21">
         <f t="shared" si="2"/>
-        <v>4350</v>
+        <v>0</v>
       </c>
       <c r="K43" s="21">
         <f t="shared" si="3"/>
         <v>38250</v>
       </c>
-      <c r="L43" s="73"/>
+      <c r="L43" s="71"/>
       <c r="M43" s="3">
         <f t="shared" si="4"/>
-        <v>127800</v>
+        <v>38250</v>
       </c>
       <c r="N43" s="7">
         <f t="shared" si="1"/>
-        <v>135468</v>
+        <v>40545</v>
       </c>
       <c r="P43" s="36">
         <f>L1-K52</f>
-        <v>1543275.9115000013</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="48" t="s">
+        <v>-176997.8278930001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
         <v>15</v>
       </c>
-      <c r="D44" s="53" t="s">
+      <c r="D44" s="51" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="4">
         <v>0.61</v>
       </c>
       <c r="F44" s="21">
-        <v>115493.33333333333</v>
-      </c>
-      <c r="G44" s="111"/>
-      <c r="H44" s="51">
+        <v>183634.4</v>
+      </c>
+      <c r="G44" s="109">
+        <f t="shared" si="7"/>
+        <v>183634.4</v>
+      </c>
+      <c r="H44" s="49">
         <f t="shared" si="0"/>
-        <v>115493.33333333333</v>
+        <v>0</v>
       </c>
       <c r="I44" s="34"/>
       <c r="J44" s="21">
         <f t="shared" si="2"/>
-        <v>5896.6666666666661</v>
+        <v>0</v>
       </c>
       <c r="K44" s="21">
         <f t="shared" si="3"/>
         <v>51850</v>
       </c>
-      <c r="L44" s="73"/>
+      <c r="L44" s="71"/>
       <c r="M44" s="3">
         <f t="shared" si="4"/>
-        <v>173240</v>
+        <v>51850</v>
       </c>
       <c r="N44" s="7">
         <f t="shared" si="1"/>
-        <v>183634.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="48" t="s">
+        <v>54961</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
         <v>16</v>
       </c>
-      <c r="D45" s="53" t="s">
+      <c r="D45" s="51" t="s">
         <v>45</v>
       </c>
       <c r="E45" s="4">
         <v>0.54</v>
       </c>
       <c r="F45" s="21">
-        <v>51120</v>
-      </c>
-      <c r="G45" s="111">
-        <f t="shared" ref="G45" si="7">F45</f>
-        <v>51120</v>
-      </c>
-      <c r="H45" s="51">
+        <v>54187.199999999997</v>
+      </c>
+      <c r="G45" s="109">
+        <f t="shared" ref="G45" si="8">F45</f>
+        <v>54187.199999999997</v>
+      </c>
+      <c r="H45" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I45" s="34"/>
       <c r="J45" s="21">
         <f t="shared" si="2"/>
-        <v>5220</v>
+        <v>0</v>
       </c>
       <c r="K45" s="21">
         <f t="shared" si="3"/>
         <v>45900</v>
       </c>
-      <c r="L45" s="73"/>
+      <c r="L45" s="71"/>
       <c r="M45" s="3">
         <f t="shared" si="4"/>
-        <v>51120</v>
+        <v>45900</v>
       </c>
       <c r="N45" s="7">
         <f t="shared" si="1"/>
-        <v>54187.199999999997</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="48" t="s">
+        <v>48654</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
         <v>17</v>
       </c>
-      <c r="D46" s="53" t="s">
+      <c r="D46" s="51" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="4">
         <v>0.5</v>
       </c>
       <c r="F46" s="21">
-        <v>50173.333333333336</v>
-      </c>
-      <c r="G46" s="111">
-        <f t="shared" ref="G46:G51" si="8">F46</f>
-        <v>50173.333333333336</v>
-      </c>
-      <c r="H46" s="51">
+        <v>47333.333333333336</v>
+      </c>
+      <c r="G46" s="109">
+        <f t="shared" ref="G46:G51" si="9">F46</f>
+        <v>47333.333333333336</v>
+      </c>
+      <c r="H46" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I46" s="34"/>
       <c r="J46" s="21">
         <f t="shared" si="2"/>
-        <v>4833.333333333333</v>
+        <v>0</v>
       </c>
       <c r="K46" s="21">
         <f t="shared" si="3"/>
         <v>42500</v>
       </c>
-      <c r="L46" s="73"/>
+      <c r="L46" s="71"/>
       <c r="M46" s="3">
         <f t="shared" si="4"/>
-        <v>47333.333333333336</v>
+        <v>42500</v>
       </c>
       <c r="N46" s="7">
         <f t="shared" si="1"/>
-        <v>50173.333333333336</v>
+        <v>45050</v>
       </c>
       <c r="Q46" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="48" t="s">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
         <v>18</v>
       </c>
-      <c r="D47" s="53" t="s">
+      <c r="D47" s="51" t="s">
         <v>39</v>
       </c>
       <c r="E47" s="4">
@@ -5621,47 +5762,47 @@
       <c r="F47" s="21">
         <v>47333.333333333336</v>
       </c>
-      <c r="G47" s="111">
-        <f t="shared" si="8"/>
+      <c r="G47" s="109">
+        <f t="shared" si="9"/>
         <v>47333.333333333336</v>
       </c>
-      <c r="H47" s="51">
+      <c r="H47" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I47" s="34"/>
       <c r="J47" s="21">
         <f t="shared" si="2"/>
-        <v>4833.333333333333</v>
+        <v>0</v>
       </c>
       <c r="K47" s="21">
         <f t="shared" si="3"/>
         <v>42500</v>
       </c>
-      <c r="L47" s="73"/>
+      <c r="L47" s="71"/>
       <c r="M47" s="3">
         <f t="shared" si="4"/>
-        <v>47333.333333333336</v>
+        <v>42500</v>
       </c>
       <c r="N47" s="7">
         <f t="shared" si="1"/>
-        <v>50173.333333333336</v>
-      </c>
-      <c r="O47" s="58"/>
-      <c r="Q47" s="55">
+        <v>45050</v>
+      </c>
+      <c r="O47" s="56"/>
+      <c r="Q47" s="53">
         <f>M3-J52</f>
-        <v>-888463.33333333314</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="48" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
         <v>19</v>
       </c>
-      <c r="D48" s="53" t="s">
+      <c r="D48" s="51" t="s">
         <v>39</v>
       </c>
       <c r="E48" s="4">
@@ -5670,42 +5811,42 @@
       <c r="F48" s="21">
         <v>46386.666666666664</v>
       </c>
-      <c r="G48" s="111">
-        <f t="shared" si="8"/>
+      <c r="G48" s="109">
+        <f t="shared" si="9"/>
         <v>46386.666666666664</v>
       </c>
-      <c r="H48" s="51">
+      <c r="H48" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I48" s="34"/>
       <c r="J48" s="21">
         <f t="shared" si="2"/>
-        <v>4736.6666666666661</v>
+        <v>0</v>
       </c>
       <c r="K48" s="21">
         <f t="shared" si="3"/>
         <v>41650</v>
       </c>
-      <c r="L48" s="73"/>
+      <c r="L48" s="71"/>
       <c r="M48" s="3">
         <f t="shared" si="4"/>
-        <v>46386.666666666664</v>
+        <v>41650</v>
       </c>
       <c r="N48" s="7">
         <f t="shared" si="1"/>
-        <v>49169.866666666661</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="48" t="s">
+        <v>44149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
         <v>20</v>
       </c>
-      <c r="D49" s="53" t="str">
+      <c r="D49" s="51" t="str">
         <f>D16</f>
         <v>FEUILLANT, GASTON</v>
       </c>
@@ -5715,42 +5856,42 @@
       <c r="F49" s="21">
         <v>46386.666666666664</v>
       </c>
-      <c r="G49" s="111">
-        <f t="shared" si="8"/>
+      <c r="G49" s="109">
+        <f t="shared" si="9"/>
         <v>46386.666666666664</v>
       </c>
-      <c r="H49" s="51">
+      <c r="H49" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I49" s="34"/>
       <c r="J49" s="21">
         <f t="shared" si="2"/>
-        <v>4736.6666666666661</v>
+        <v>0</v>
       </c>
       <c r="K49" s="21">
         <f t="shared" si="3"/>
         <v>41650</v>
       </c>
-      <c r="L49" s="73"/>
+      <c r="L49" s="71"/>
       <c r="M49" s="3">
         <f t="shared" si="4"/>
-        <v>46386.666666666664</v>
+        <v>41650</v>
       </c>
       <c r="N49" s="7">
         <f t="shared" si="1"/>
-        <v>49169.866666666661</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" s="48" t="s">
+        <v>44149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
         <v>21</v>
       </c>
-      <c r="D50" s="53" t="s">
+      <c r="D50" s="51" t="s">
         <v>35</v>
       </c>
       <c r="E50" s="4">
@@ -5759,42 +5900,42 @@
       <c r="F50" s="21">
         <v>55853.333333333336</v>
       </c>
-      <c r="G50" s="112">
-        <f t="shared" si="8"/>
+      <c r="G50" s="110">
+        <f t="shared" si="9"/>
         <v>55853.333333333336</v>
       </c>
-      <c r="H50" s="51">
+      <c r="H50" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I50" s="34"/>
       <c r="J50" s="21">
         <f t="shared" si="2"/>
-        <v>5703.333333333333</v>
+        <v>0</v>
       </c>
       <c r="K50" s="21">
         <f t="shared" si="3"/>
         <v>50150</v>
       </c>
-      <c r="L50" s="73"/>
+      <c r="L50" s="71"/>
       <c r="M50" s="3">
         <f t="shared" si="4"/>
-        <v>55853.333333333336</v>
+        <v>50150</v>
       </c>
       <c r="N50" s="7">
         <f t="shared" si="1"/>
-        <v>59204.533333333333</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="48" t="s">
+        <v>53159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="47" t="s">
         <v>69</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
         <v>22</v>
       </c>
-      <c r="D51" s="53" t="s">
+      <c r="D51" s="51" t="s">
         <v>41</v>
       </c>
       <c r="E51" s="4">
@@ -5803,34 +5944,34 @@
       <c r="F51" s="21">
         <v>53960</v>
       </c>
-      <c r="G51" s="111">
-        <f t="shared" si="8"/>
+      <c r="G51" s="109">
+        <f t="shared" si="9"/>
         <v>53960</v>
       </c>
-      <c r="H51" s="51">
+      <c r="H51" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I51" s="34"/>
       <c r="J51" s="21">
         <f t="shared" si="2"/>
-        <v>5509.9999999999991</v>
+        <v>0</v>
       </c>
       <c r="K51" s="21">
         <f t="shared" si="3"/>
         <v>48450</v>
       </c>
-      <c r="L51" s="73"/>
+      <c r="L51" s="71"/>
       <c r="M51" s="3">
         <f t="shared" si="4"/>
-        <v>53960</v>
+        <v>48450</v>
       </c>
       <c r="N51" s="7">
         <f t="shared" si="1"/>
-        <v>57197.599999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>51357</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -5839,188 +5980,190 @@
         <f>SUM(E7:E51)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F52" s="91">
+      <c r="F52" s="89">
         <f>SUM(F7:F51)</f>
-        <v>9232672.8804826699</v>
-      </c>
-      <c r="G52" s="91">
+        <v>11508062.463274701</v>
+      </c>
+      <c r="G52" s="89">
         <f>SUM(G7:G51)</f>
-        <v>7423417.4468569998</v>
+        <v>12695174.355166664</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="22"/>
-      <c r="J52" s="49">
+      <c r="J52" s="48">
         <f>SUM(J8:J51)</f>
-        <v>888463.33333333314</v>
+        <v>0</v>
       </c>
       <c r="K52" s="23">
         <f>SUM(K7:K51)</f>
-        <v>8427251.8884999994</v>
-      </c>
-      <c r="L52" s="93">
+        <v>8274595.1878929995</v>
+      </c>
+      <c r="L52" s="91">
         <f>SUM(L7:L51)</f>
-        <v>165775</v>
+        <v>40000</v>
       </c>
       <c r="M52" s="24">
         <f>SUM(M7:M51)</f>
-        <v>11290745.655459</v>
+        <v>7127483.2960010357</v>
       </c>
       <c r="N52" s="23">
         <f>SUM(N7:N51)</f>
-        <v>11968190.394786539</v>
-      </c>
-      <c r="P52" s="55"/>
-    </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="K53" s="58">
+        <v>7555132.2937610988</v>
+      </c>
+      <c r="P52" s="53"/>
+    </row>
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K53" s="56">
         <f>K52-L1</f>
-        <v>-1543275.9115000013</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="205"/>
-      <c r="D54" s="205"/>
-      <c r="E54" s="205"/>
-      <c r="F54" s="205"/>
-      <c r="G54" s="205"/>
-      <c r="H54" s="205"/>
-      <c r="I54" s="205"/>
-      <c r="J54" s="205"/>
-      <c r="K54" s="205"/>
-      <c r="L54" s="205"/>
-      <c r="M54" s="205"/>
-      <c r="N54" s="205"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="205"/>
-      <c r="D55" s="205"/>
-      <c r="E55" s="205"/>
-      <c r="F55" s="205"/>
-      <c r="G55" s="205"/>
-      <c r="H55" s="205"/>
-      <c r="I55" s="205"/>
-      <c r="J55" s="205"/>
-      <c r="K55" s="205"/>
-      <c r="L55" s="205"/>
-      <c r="M55" s="205"/>
-      <c r="N55" s="205"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="75"/>
-      <c r="G56" s="75"/>
-      <c r="H56" s="75"/>
-      <c r="I56" s="75"/>
-      <c r="J56" s="75"/>
-      <c r="K56" s="75"/>
-      <c r="L56" s="75"/>
-      <c r="M56" s="75"/>
-      <c r="N56" s="75"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="205" t="s">
+        <v>176997.8278930001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="172"/>
+      <c r="D54" s="172"/>
+      <c r="E54" s="172"/>
+      <c r="F54" s="172"/>
+      <c r="G54" s="172"/>
+      <c r="H54" s="172"/>
+      <c r="I54" s="172"/>
+      <c r="J54" s="172"/>
+      <c r="K54" s="172"/>
+      <c r="L54" s="172"/>
+      <c r="M54" s="172"/>
+      <c r="N54" s="172"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="172"/>
+      <c r="D55" s="172"/>
+      <c r="E55" s="172"/>
+      <c r="F55" s="172"/>
+      <c r="G55" s="172"/>
+      <c r="H55" s="172"/>
+      <c r="I55" s="172"/>
+      <c r="J55" s="172"/>
+      <c r="K55" s="172"/>
+      <c r="L55" s="172"/>
+      <c r="M55" s="172"/>
+      <c r="N55" s="172"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73"/>
+      <c r="J56" s="73"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="73"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="73"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="D57" s="205"/>
-      <c r="E57" s="205"/>
-      <c r="F57" s="205"/>
-      <c r="G57" s="205"/>
-      <c r="H57" s="205"/>
-      <c r="I57" s="205"/>
-      <c r="J57" s="205"/>
-      <c r="K57" s="205"/>
-      <c r="L57" s="205"/>
-      <c r="M57" s="205"/>
-      <c r="N57" s="205"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="205"/>
-      <c r="D58" s="205"/>
-      <c r="E58" s="205"/>
-      <c r="F58" s="205"/>
-      <c r="G58" s="205"/>
-      <c r="H58" s="205"/>
-      <c r="I58" s="205"/>
-      <c r="J58" s="205"/>
-      <c r="K58" s="205"/>
-      <c r="L58" s="205"/>
-      <c r="M58" s="205"/>
-      <c r="N58" s="205"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="205"/>
-      <c r="D59" s="205"/>
-      <c r="E59" s="205"/>
-      <c r="F59" s="205"/>
-      <c r="G59" s="205"/>
-      <c r="H59" s="205"/>
-      <c r="I59" s="205"/>
-      <c r="J59" s="205"/>
-      <c r="K59" s="205"/>
-      <c r="L59" s="205"/>
-      <c r="M59" s="205"/>
-      <c r="N59" s="205"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="205"/>
-      <c r="D60" s="205"/>
-      <c r="E60" s="205"/>
-      <c r="F60" s="205"/>
-      <c r="G60" s="205"/>
-      <c r="H60" s="205"/>
-      <c r="I60" s="205"/>
-      <c r="J60" s="205"/>
-      <c r="K60" s="205"/>
-      <c r="L60" s="205"/>
-      <c r="M60" s="205"/>
-      <c r="N60" s="205"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="205"/>
-      <c r="D61" s="205"/>
-      <c r="E61" s="205"/>
-      <c r="F61" s="205"/>
-      <c r="G61" s="205"/>
-      <c r="H61" s="205"/>
-      <c r="I61" s="205"/>
-      <c r="J61" s="205"/>
-      <c r="K61" s="205"/>
-      <c r="L61" s="205"/>
-      <c r="M61" s="205"/>
-      <c r="N61" s="205"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="205"/>
-      <c r="D62" s="205"/>
-      <c r="E62" s="205"/>
-      <c r="F62" s="205"/>
-      <c r="G62" s="205"/>
-      <c r="H62" s="205"/>
-      <c r="I62" s="205"/>
-      <c r="J62" s="205"/>
-      <c r="K62" s="205"/>
-      <c r="L62" s="205"/>
-      <c r="M62" s="205"/>
-      <c r="N62" s="205"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="205"/>
-      <c r="D63" s="205"/>
-      <c r="E63" s="205"/>
-      <c r="F63" s="205"/>
-      <c r="G63" s="205"/>
-      <c r="H63" s="205"/>
-      <c r="I63" s="205"/>
-      <c r="J63" s="205"/>
-      <c r="K63" s="205"/>
-      <c r="L63" s="205"/>
-      <c r="M63" s="205"/>
-      <c r="N63" s="205"/>
+      <c r="D57" s="172"/>
+      <c r="E57" s="172"/>
+      <c r="F57" s="172"/>
+      <c r="G57" s="172"/>
+      <c r="H57" s="172"/>
+      <c r="I57" s="172"/>
+      <c r="J57" s="172"/>
+      <c r="K57" s="172"/>
+      <c r="L57" s="172"/>
+      <c r="M57" s="172"/>
+      <c r="N57" s="172"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="172"/>
+      <c r="D58" s="172"/>
+      <c r="E58" s="172"/>
+      <c r="F58" s="172"/>
+      <c r="G58" s="172"/>
+      <c r="H58" s="172"/>
+      <c r="I58" s="172"/>
+      <c r="J58" s="172"/>
+      <c r="K58" s="172"/>
+      <c r="L58" s="172"/>
+      <c r="M58" s="172"/>
+      <c r="N58" s="172"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="172"/>
+      <c r="D59" s="172"/>
+      <c r="E59" s="172"/>
+      <c r="F59" s="172"/>
+      <c r="G59" s="172"/>
+      <c r="H59" s="172"/>
+      <c r="I59" s="172"/>
+      <c r="J59" s="172"/>
+      <c r="K59" s="172"/>
+      <c r="L59" s="172"/>
+      <c r="M59" s="172"/>
+      <c r="N59" s="172"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="172"/>
+      <c r="D60" s="172"/>
+      <c r="E60" s="172"/>
+      <c r="F60" s="172"/>
+      <c r="G60" s="172"/>
+      <c r="H60" s="172"/>
+      <c r="I60" s="172"/>
+      <c r="J60" s="172"/>
+      <c r="K60" s="172"/>
+      <c r="L60" s="172"/>
+      <c r="M60" s="172"/>
+      <c r="N60" s="172"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="172"/>
+      <c r="D61" s="172"/>
+      <c r="E61" s="172"/>
+      <c r="F61" s="172"/>
+      <c r="G61" s="172"/>
+      <c r="H61" s="172"/>
+      <c r="I61" s="172"/>
+      <c r="J61" s="172"/>
+      <c r="K61" s="172"/>
+      <c r="L61" s="172"/>
+      <c r="M61" s="172"/>
+      <c r="N61" s="172"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="172"/>
+      <c r="D62" s="172"/>
+      <c r="E62" s="172"/>
+      <c r="F62" s="172"/>
+      <c r="G62" s="172"/>
+      <c r="H62" s="172"/>
+      <c r="I62" s="172"/>
+      <c r="J62" s="172"/>
+      <c r="K62" s="172"/>
+      <c r="L62" s="172"/>
+      <c r="M62" s="172"/>
+      <c r="N62" s="172"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="172"/>
+      <c r="D63" s="172"/>
+      <c r="E63" s="172"/>
+      <c r="F63" s="172"/>
+      <c r="G63" s="172"/>
+      <c r="H63" s="172"/>
+      <c r="I63" s="172"/>
+      <c r="J63" s="172"/>
+      <c r="K63" s="172"/>
+      <c r="L63" s="172"/>
+      <c r="M63" s="172"/>
+      <c r="N63" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6037,8 +6180,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6048,11 +6189,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2666E70F-CDC7-456F-AF96-2906778A9145}">
   <dimension ref="C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
